--- a/spreadsheet.xlsx
+++ b/spreadsheet.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loren\Desktop\MK1212-website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD650006-643E-4D05-BF48-77B3E2C73D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00297FC-E32F-44E2-B2AA-C22C0FF1DD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2003C0B9-FD41-4D78-AC63-D37F7559A3C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$D$552</definedName>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="859">
   <si>
     <t>false</t>
   </si>
@@ -1464,9 +1463,6 @@
     <t>Aden</t>
   </si>
   <si>
-    <t>Agadir</t>
-  </si>
-  <si>
     <t>Ahvaz</t>
   </si>
   <si>
@@ -1566,9 +1562,6 @@
     <t>Bilyar</t>
   </si>
   <si>
-    <t>Biskra</t>
-  </si>
-  <si>
     <t>Bologna</t>
   </si>
   <si>
@@ -1614,9 +1607,6 @@
     <t>Candia</t>
   </si>
   <si>
-    <t>Cardiff</t>
-  </si>
-  <si>
     <t>Chernigov</t>
   </si>
   <si>
@@ -1842,9 +1832,6 @@
     <t>Mecca</t>
   </si>
   <si>
-    <t>Mersa Matruh</t>
-  </si>
-  <si>
     <t>Merv</t>
   </si>
   <si>
@@ -1914,9 +1901,6 @@
     <t>Oslo</t>
   </si>
   <si>
-    <t>Pahrah</t>
-  </si>
-  <si>
     <t>Palermo</t>
   </si>
   <si>
@@ -2001,9 +1985,6 @@
     <t>Sale</t>
   </si>
   <si>
-    <t>Salzburg</t>
-  </si>
-  <si>
     <t>Samarkand</t>
   </si>
   <si>
@@ -2013,9 +1994,6 @@
     <t>Saqsin</t>
   </si>
   <si>
-    <t>Sarkel</t>
-  </si>
-  <si>
     <t>Scopie</t>
   </si>
   <si>
@@ -2196,9 +2174,6 @@
     <t>Baltic Sea</t>
   </si>
   <si>
-    <t>Black Sea</t>
-  </si>
-  <si>
     <t>Caspian Sea</t>
   </si>
   <si>
@@ -2220,30 +2195,6 @@
     <t>Western Mediterranean</t>
   </si>
   <si>
-    <t>mk_reg_agadir</t>
-  </si>
-  <si>
-    <t>mk_reg_biskra</t>
-  </si>
-  <si>
-    <t>mk_reg_cardiff</t>
-  </si>
-  <si>
-    <t>mk_reg_mersa_matruh</t>
-  </si>
-  <si>
-    <t>mk_reg_pahrah</t>
-  </si>
-  <si>
-    <t>mk_reg_salzburg</t>
-  </si>
-  <si>
-    <t>mk_reg_sarkel</t>
-  </si>
-  <si>
-    <t>mk_sea_black_sea</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -2407,6 +2358,264 @@
   </si>
   <si>
     <t>Region_Key</t>
+  </si>
+  <si>
+    <t>mk_fact_ayyubids</t>
+  </si>
+  <si>
+    <t>mk_fact_zengids</t>
+  </si>
+  <si>
+    <t>mk_fact_abbasids</t>
+  </si>
+  <si>
+    <t>mk_fact_denmark</t>
+  </si>
+  <si>
+    <t>mk_fact_provence</t>
+  </si>
+  <si>
+    <t>mk_fact_genoa</t>
+  </si>
+  <si>
+    <t>mk_fact_hafsids</t>
+  </si>
+  <si>
+    <t>mk_fact_almohads</t>
+  </si>
+  <si>
+    <t>mk_fact_khwarazm</t>
+  </si>
+  <si>
+    <t>mk_fact_ancona</t>
+  </si>
+  <si>
+    <t>mk_fact_brabant</t>
+  </si>
+  <si>
+    <t>mk_fact_athens</t>
+  </si>
+  <si>
+    <t>mk_fact_oman</t>
+  </si>
+  <si>
+    <t>mk_fact_shirvan</t>
+  </si>
+  <si>
+    <t>mk_fact_aragon</t>
+  </si>
+  <si>
+    <t>mk_fact_serbia</t>
+  </si>
+  <si>
+    <t>mk_fact_schwyz</t>
+  </si>
+  <si>
+    <t>mk_fact_kiev</t>
+  </si>
+  <si>
+    <t>mk_fact_bologna</t>
+  </si>
+  <si>
+    <t>mk_fact_england</t>
+  </si>
+  <si>
+    <t>mk_fact_portugal</t>
+  </si>
+  <si>
+    <t>mk_fact_brandenburg</t>
+  </si>
+  <si>
+    <t>mk_fact_hre</t>
+  </si>
+  <si>
+    <t>mk_fact_flanders</t>
+  </si>
+  <si>
+    <t>mk_fact_wales</t>
+  </si>
+  <si>
+    <t>mk_fact_pisa</t>
+  </si>
+  <si>
+    <t>mk_fact_venice</t>
+  </si>
+  <si>
+    <t>mk_fact_chernigov</t>
+  </si>
+  <si>
+    <t>mk_fact_nicaea</t>
+  </si>
+  <si>
+    <t>mk_fact_burgundy</t>
+  </si>
+  <si>
+    <t>mk_fact_makuria</t>
+  </si>
+  <si>
+    <t>mk_fact_sicily</t>
+  </si>
+  <si>
+    <t>mk_fact_ireland</t>
+  </si>
+  <si>
+    <t>mk_fact_georgia</t>
+  </si>
+  <si>
+    <t>mk_fact_scotland</t>
+  </si>
+  <si>
+    <t>mk_fact_seljuks</t>
+  </si>
+  <si>
+    <t>mk_fact_hungary</t>
+  </si>
+  <si>
+    <t>mk_fact_yotvingians</t>
+  </si>
+  <si>
+    <t>mk_fact_austria</t>
+  </si>
+  <si>
+    <t>mk_fact_friesland</t>
+  </si>
+  <si>
+    <t>mk_fact_halych</t>
+  </si>
+  <si>
+    <t>mk_fact_bavaria</t>
+  </si>
+  <si>
+    <t>mk_fact_lesserpoland</t>
+  </si>
+  <si>
+    <t>mk_fact_zagwe</t>
+  </si>
+  <si>
+    <t>mk_fact_sweden</t>
+  </si>
+  <si>
+    <t>mk_fact_france</t>
+  </si>
+  <si>
+    <t>mk_fact_alania</t>
+  </si>
+  <si>
+    <t>mk_fact_mecca</t>
+  </si>
+  <si>
+    <t>mk_fact_milan</t>
+  </si>
+  <si>
+    <t>mk_fact_toulouse</t>
+  </si>
+  <si>
+    <t>mk_fact_lorraine</t>
+  </si>
+  <si>
+    <t>mk_fact_navarre</t>
+  </si>
+  <si>
+    <t>mk_fact_greaterpoland</t>
+  </si>
+  <si>
+    <t>mk_fact_bohemia</t>
+  </si>
+  <si>
+    <t>mk_fact_papacy</t>
+  </si>
+  <si>
+    <t>mk_fact_bulgaria</t>
+  </si>
+  <si>
+    <t>mk_fact_croatia</t>
+  </si>
+  <si>
+    <t>mk_fact_marinids</t>
+  </si>
+  <si>
+    <t>mk_fact_wallachia</t>
+  </si>
+  <si>
+    <t>mk_fact_castile</t>
+  </si>
+  <si>
+    <t>mk_fact_trebizond</t>
+  </si>
+  <si>
+    <t>mk_fact_trier</t>
+  </si>
+  <si>
+    <t>mk_fact_savoy</t>
+  </si>
+  <si>
+    <t>mk_fact_verona</t>
+  </si>
+  <si>
+    <t>mk_fact_dauphine</t>
+  </si>
+  <si>
+    <t>mk_fact_lithuania</t>
+  </si>
+  <si>
+    <t>mk_fact_saxony</t>
+  </si>
+  <si>
+    <t>mk_fact_silesia</t>
+  </si>
+  <si>
+    <t>mk_fact_epirus</t>
+  </si>
+  <si>
+    <t>mk_fact_achaea</t>
+  </si>
+  <si>
+    <t>mk_fact_thessalonica</t>
+  </si>
+  <si>
+    <t>mk_fact_latinempire</t>
+  </si>
+  <si>
+    <t>mk_fact_ghurids</t>
+  </si>
+  <si>
+    <t>mk_fact_hazaraspids</t>
+  </si>
+  <si>
+    <t>mk_fact_salghurids</t>
+  </si>
+  <si>
+    <t>mk_fact_ildegizids</t>
+  </si>
+  <si>
+    <t>mk_fact_vladimir</t>
+  </si>
+  <si>
+    <t>mk_fact_volga</t>
+  </si>
+  <si>
+    <t>mk_fact_cumans</t>
+  </si>
+  <si>
+    <t>mk_fact_pomerania</t>
+  </si>
+  <si>
+    <t>mk_fact_teutonicorder</t>
+  </si>
+  <si>
+    <t>mk_fact_armenia</t>
+  </si>
+  <si>
+    <t>mk_fact_antioch</t>
+  </si>
+  <si>
+    <t>mk_fact_jerusalem</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Impassable</t>
   </si>
 </sst>
 </file>
@@ -2781,7 +2990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB689665-45D9-42F4-AA4C-1FD1A1AE5053}">
-  <dimension ref="A1:D257"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.5703125" bestFit="1" customWidth="1"/>
@@ -2789,9 +2998,9 @@
     <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="B1" t="s">
         <v>469</v>
@@ -2800,10 +3009,13 @@
         <v>470</v>
       </c>
       <c r="D1" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>718</v>
+      </c>
+      <c r="E1" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>178</v>
       </c>
@@ -2816,8 +3028,11 @@
       <c r="D2" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>179</v>
       </c>
@@ -2825,13 +3040,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D3" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>180</v>
       </c>
@@ -2844,8 +3062,11 @@
       <c r="D4" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>181</v>
       </c>
@@ -2856,10 +3077,13 @@
         <v>182</v>
       </c>
       <c r="D5" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>474</v>
+      </c>
+      <c r="E5" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>183</v>
       </c>
@@ -2870,10 +3094,13 @@
         <v>154</v>
       </c>
       <c r="D6" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+      <c r="E6" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>184</v>
       </c>
@@ -2884,10 +3111,13 @@
         <v>148</v>
       </c>
       <c r="D7" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>476</v>
+      </c>
+      <c r="E7" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>185</v>
       </c>
@@ -2895,13 +3125,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="D8" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>477</v>
+      </c>
+      <c r="E8" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>186</v>
       </c>
@@ -2912,10 +3145,13 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>478</v>
+      </c>
+      <c r="E9" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>187</v>
       </c>
@@ -2926,10 +3162,13 @@
         <v>140</v>
       </c>
       <c r="D10" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>479</v>
+      </c>
+      <c r="E10" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>188</v>
       </c>
@@ -2940,10 +3179,13 @@
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+      <c r="E11" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>189</v>
       </c>
@@ -2954,10 +3196,13 @@
         <v>190</v>
       </c>
       <c r="D12" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>481</v>
+      </c>
+      <c r="E12" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>191</v>
       </c>
@@ -2968,10 +3213,13 @@
         <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>482</v>
+      </c>
+      <c r="E13" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>192</v>
       </c>
@@ -2982,10 +3230,13 @@
         <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>483</v>
+      </c>
+      <c r="E14" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>193</v>
       </c>
@@ -2993,13 +3244,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>745</v>
+        <v>729</v>
       </c>
       <c r="D15" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+      <c r="E15" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>194</v>
       </c>
@@ -3010,10 +3264,13 @@
         <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>485</v>
+      </c>
+      <c r="E16" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>195</v>
       </c>
@@ -3024,10 +3281,13 @@
         <v>196</v>
       </c>
       <c r="D17" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>486</v>
+      </c>
+      <c r="E17" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>197</v>
       </c>
@@ -3038,10 +3298,13 @@
         <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>487</v>
+      </c>
+      <c r="E18" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>198</v>
       </c>
@@ -3052,10 +3315,13 @@
         <v>160</v>
       </c>
       <c r="D19" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>488</v>
+      </c>
+      <c r="E19" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>199</v>
       </c>
@@ -3066,10 +3332,13 @@
         <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+      <c r="E20" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>200</v>
       </c>
@@ -3080,10 +3349,13 @@
         <v>201</v>
       </c>
       <c r="D21" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>490</v>
+      </c>
+      <c r="E21" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>202</v>
       </c>
@@ -3091,13 +3363,16 @@
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>746</v>
+        <v>730</v>
       </c>
       <c r="D22" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>491</v>
+      </c>
+      <c r="E22" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>203</v>
       </c>
@@ -3108,10 +3383,13 @@
         <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>492</v>
+      </c>
+      <c r="E23" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>204</v>
       </c>
@@ -3122,10 +3400,13 @@
         <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>493</v>
+      </c>
+      <c r="E24" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>205</v>
       </c>
@@ -3136,10 +3417,13 @@
         <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+      <c r="E25" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>206</v>
       </c>
@@ -3150,10 +3434,13 @@
         <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>495</v>
+      </c>
+      <c r="E26" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>207</v>
       </c>
@@ -3164,10 +3451,13 @@
         <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>496</v>
+      </c>
+      <c r="E27" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>208</v>
       </c>
@@ -3178,10 +3468,13 @@
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>497</v>
+      </c>
+      <c r="E28" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>209</v>
       </c>
@@ -3189,13 +3482,16 @@
         <v>0</v>
       </c>
       <c r="C29" t="s">
-        <v>747</v>
+        <v>731</v>
       </c>
       <c r="D29" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+      <c r="E29" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>210</v>
       </c>
@@ -3206,10 +3502,13 @@
         <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>499</v>
+      </c>
+      <c r="E30" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>211</v>
       </c>
@@ -3220,10 +3519,13 @@
         <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+      <c r="E31" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>212</v>
       </c>
@@ -3234,10 +3536,13 @@
         <v>64</v>
       </c>
       <c r="D32" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>501</v>
+      </c>
+      <c r="E32" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>213</v>
       </c>
@@ -3248,10 +3553,13 @@
         <v>163</v>
       </c>
       <c r="D33" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>502</v>
+      </c>
+      <c r="E33" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>214</v>
       </c>
@@ -3262,10 +3570,13 @@
         <v>215</v>
       </c>
       <c r="D34" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>503</v>
+      </c>
+      <c r="E34" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>216</v>
       </c>
@@ -3276,10 +3587,13 @@
         <v>143</v>
       </c>
       <c r="D35" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>504</v>
+      </c>
+      <c r="E35" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>217</v>
       </c>
@@ -3290,10 +3604,13 @@
         <v>176</v>
       </c>
       <c r="D36" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>505</v>
+      </c>
+      <c r="E36" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>218</v>
       </c>
@@ -3304,10 +3621,13 @@
         <v>219</v>
       </c>
       <c r="D37" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="E37" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>220</v>
       </c>
@@ -3318,10 +3638,13 @@
         <v>23</v>
       </c>
       <c r="D38" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+      <c r="E38" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>221</v>
       </c>
@@ -3332,10 +3655,13 @@
         <v>59</v>
       </c>
       <c r="D39" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+      <c r="E39" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>222</v>
       </c>
@@ -3346,10 +3672,13 @@
         <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>509</v>
+      </c>
+      <c r="E40" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>223</v>
       </c>
@@ -3360,10 +3689,13 @@
         <v>103</v>
       </c>
       <c r="D41" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+      <c r="E41" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>224</v>
       </c>
@@ -3374,10 +3706,13 @@
         <v>98</v>
       </c>
       <c r="D42" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+      <c r="E42" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>225</v>
       </c>
@@ -3388,10 +3723,13 @@
         <v>41</v>
       </c>
       <c r="D43" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+      <c r="E43" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>226</v>
       </c>
@@ -3402,10 +3740,13 @@
         <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+      <c r="E44" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>227</v>
       </c>
@@ -3413,13 +3754,16 @@
         <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
       <c r="D45" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+      <c r="E45" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>228</v>
       </c>
@@ -3427,13 +3771,16 @@
         <v>0</v>
       </c>
       <c r="C46" t="s">
-        <v>749</v>
+        <v>733</v>
       </c>
       <c r="D46" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+      <c r="E46" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>229</v>
       </c>
@@ -3444,10 +3791,13 @@
         <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+      <c r="E47" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>230</v>
       </c>
@@ -3458,10 +3808,13 @@
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+      <c r="E48" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>231</v>
       </c>
@@ -3472,10 +3825,13 @@
         <v>174</v>
       </c>
       <c r="D49" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+      <c r="E49" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>232</v>
       </c>
@@ -3486,10 +3842,13 @@
         <v>149</v>
       </c>
       <c r="D50" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+      <c r="E50" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>233</v>
       </c>
@@ -3497,13 +3856,16 @@
         <v>0</v>
       </c>
       <c r="C51" t="s">
-        <v>750</v>
+        <v>734</v>
       </c>
       <c r="D51" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="E51" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>234</v>
       </c>
@@ -3514,10 +3876,13 @@
         <v>152</v>
       </c>
       <c r="D52" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>521</v>
+      </c>
+      <c r="E52" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>235</v>
       </c>
@@ -3528,10 +3893,13 @@
         <v>114</v>
       </c>
       <c r="D53" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+      <c r="E53" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>236</v>
       </c>
@@ -3542,10 +3910,13 @@
         <v>43</v>
       </c>
       <c r="D54" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>523</v>
+      </c>
+      <c r="E54" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>237</v>
       </c>
@@ -3556,10 +3927,13 @@
         <v>48</v>
       </c>
       <c r="D55" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>524</v>
+      </c>
+      <c r="E55" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>238</v>
       </c>
@@ -3570,10 +3944,13 @@
         <v>73</v>
       </c>
       <c r="D56" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>525</v>
+      </c>
+      <c r="E56" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>239</v>
       </c>
@@ -3581,13 +3958,16 @@
         <v>0</v>
       </c>
       <c r="C57" t="s">
-        <v>751</v>
+        <v>735</v>
       </c>
       <c r="D57" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+      <c r="E57" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>240</v>
       </c>
@@ -3598,10 +3978,13 @@
         <v>87</v>
       </c>
       <c r="D58" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+      <c r="E58" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>241</v>
       </c>
@@ -3612,10 +3995,13 @@
         <v>161</v>
       </c>
       <c r="D59" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>528</v>
+      </c>
+      <c r="E59" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>242</v>
       </c>
@@ -3623,13 +4009,16 @@
         <v>0</v>
       </c>
       <c r="C60" t="s">
-        <v>752</v>
+        <v>736</v>
       </c>
       <c r="D60" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+        <v>529</v>
+      </c>
+      <c r="E60" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>243</v>
       </c>
@@ -3637,13 +4026,16 @@
         <v>0</v>
       </c>
       <c r="C61" t="s">
-        <v>753</v>
+        <v>737</v>
       </c>
       <c r="D61" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>530</v>
+      </c>
+      <c r="E61" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>244</v>
       </c>
@@ -3654,10 +4046,13 @@
         <v>172</v>
       </c>
       <c r="D62" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+      <c r="E62" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>245</v>
       </c>
@@ -3668,10 +4063,13 @@
         <v>144</v>
       </c>
       <c r="D63" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>532</v>
+      </c>
+      <c r="E63" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>246</v>
       </c>
@@ -3682,10 +4080,13 @@
         <v>247</v>
       </c>
       <c r="D64" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+        <v>533</v>
+      </c>
+      <c r="E64" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>248</v>
       </c>
@@ -3696,10 +4097,13 @@
         <v>74</v>
       </c>
       <c r="D65" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+        <v>534</v>
+      </c>
+      <c r="E65" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>249</v>
       </c>
@@ -3710,10 +4114,13 @@
         <v>89</v>
       </c>
       <c r="D66" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+      <c r="E66" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>250</v>
       </c>
@@ -3724,10 +4131,13 @@
         <v>5</v>
       </c>
       <c r="D67" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+        <v>536</v>
+      </c>
+      <c r="E67" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>251</v>
       </c>
@@ -3738,10 +4148,13 @@
         <v>84</v>
       </c>
       <c r="D68" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+        <v>537</v>
+      </c>
+      <c r="E68" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>252</v>
       </c>
@@ -3752,10 +4165,13 @@
         <v>133</v>
       </c>
       <c r="D69" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+      <c r="E69" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>253</v>
       </c>
@@ -3766,10 +4182,13 @@
         <v>6</v>
       </c>
       <c r="D70" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+        <v>539</v>
+      </c>
+      <c r="E70" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>254</v>
       </c>
@@ -3780,10 +4199,13 @@
         <v>63</v>
       </c>
       <c r="D71" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+      <c r="E71" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>255</v>
       </c>
@@ -3794,10 +4216,13 @@
         <v>256</v>
       </c>
       <c r="D72" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+        <v>541</v>
+      </c>
+      <c r="E72" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>257</v>
       </c>
@@ -3805,13 +4230,16 @@
         <v>0</v>
       </c>
       <c r="C73" t="s">
-        <v>754</v>
+        <v>738</v>
       </c>
       <c r="D73" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+        <v>542</v>
+      </c>
+      <c r="E73" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>258</v>
       </c>
@@ -3822,10 +4250,13 @@
         <v>113</v>
       </c>
       <c r="D74" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+      <c r="E74" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>259</v>
       </c>
@@ -3836,10 +4267,13 @@
         <v>131</v>
       </c>
       <c r="D75" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+        <v>544</v>
+      </c>
+      <c r="E75" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>260</v>
       </c>
@@ -3850,10 +4284,13 @@
         <v>151</v>
       </c>
       <c r="D76" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+        <v>545</v>
+      </c>
+      <c r="E76" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>261</v>
       </c>
@@ -3861,13 +4298,16 @@
         <v>0</v>
       </c>
       <c r="C77" t="s">
-        <v>755</v>
+        <v>739</v>
       </c>
       <c r="D77" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+        <v>546</v>
+      </c>
+      <c r="E77" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>262</v>
       </c>
@@ -3878,10 +4318,13 @@
         <v>104</v>
       </c>
       <c r="D78" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+        <v>547</v>
+      </c>
+      <c r="E78" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>263</v>
       </c>
@@ -3892,10 +4335,13 @@
         <v>106</v>
       </c>
       <c r="D79" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+      <c r="E79" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>264</v>
       </c>
@@ -3906,10 +4352,13 @@
         <v>109</v>
       </c>
       <c r="D80" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+        <v>549</v>
+      </c>
+      <c r="E80" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>265</v>
       </c>
@@ -3920,10 +4369,13 @@
         <v>124</v>
       </c>
       <c r="D81" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+        <v>550</v>
+      </c>
+      <c r="E81" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>266</v>
       </c>
@@ -3931,13 +4383,16 @@
         <v>0</v>
       </c>
       <c r="C82" t="s">
-        <v>756</v>
+        <v>740</v>
       </c>
       <c r="D82" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+        <v>551</v>
+      </c>
+      <c r="E82" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>267</v>
       </c>
@@ -3948,10 +4403,13 @@
         <v>11</v>
       </c>
       <c r="D83" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+        <v>552</v>
+      </c>
+      <c r="E83" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>268</v>
       </c>
@@ -3962,10 +4420,13 @@
         <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+      <c r="E84" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>270</v>
       </c>
@@ -3976,10 +4437,13 @@
         <v>170</v>
       </c>
       <c r="D85" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+        <v>554</v>
+      </c>
+      <c r="E85" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>271</v>
       </c>
@@ -3990,10 +4454,13 @@
         <v>97</v>
       </c>
       <c r="D86" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+      <c r="E86" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>272</v>
       </c>
@@ -4004,10 +4471,13 @@
         <v>90</v>
       </c>
       <c r="D87" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+        <v>556</v>
+      </c>
+      <c r="E87" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>273</v>
       </c>
@@ -4018,10 +4488,13 @@
         <v>9</v>
       </c>
       <c r="D88" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+      <c r="E88" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>274</v>
       </c>
@@ -4032,10 +4505,13 @@
         <v>145</v>
       </c>
       <c r="D89" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+      <c r="E89" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>275</v>
       </c>
@@ -4046,10 +4522,13 @@
         <v>96</v>
       </c>
       <c r="D90" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+        <v>559</v>
+      </c>
+      <c r="E90" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>276</v>
       </c>
@@ -4060,10 +4539,13 @@
         <v>20</v>
       </c>
       <c r="D91" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+      <c r="E91" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>277</v>
       </c>
@@ -4074,10 +4556,13 @@
         <v>121</v>
       </c>
       <c r="D92" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+      <c r="E92" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>278</v>
       </c>
@@ -4088,10 +4573,13 @@
         <v>279</v>
       </c>
       <c r="D93" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+      <c r="E93" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>280</v>
       </c>
@@ -4102,10 +4590,13 @@
         <v>138</v>
       </c>
       <c r="D94" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+        <v>563</v>
+      </c>
+      <c r="E94" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>281</v>
       </c>
@@ -4116,10 +4607,13 @@
         <v>13</v>
       </c>
       <c r="D95" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+      <c r="E95" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>282</v>
       </c>
@@ -4130,10 +4624,13 @@
         <v>4</v>
       </c>
       <c r="D96" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>565</v>
+      </c>
+      <c r="E96" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>283</v>
       </c>
@@ -4144,10 +4641,13 @@
         <v>284</v>
       </c>
       <c r="D97" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+      <c r="E97" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>285</v>
       </c>
@@ -4158,10 +4658,13 @@
         <v>159</v>
       </c>
       <c r="D98" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>567</v>
+      </c>
+      <c r="E98" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>286</v>
       </c>
@@ -4169,13 +4672,16 @@
         <v>0</v>
       </c>
       <c r="C99" t="s">
-        <v>757</v>
+        <v>741</v>
       </c>
       <c r="D99" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+      <c r="E99" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>287</v>
       </c>
@@ -4186,10 +4692,13 @@
         <v>288</v>
       </c>
       <c r="D100" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+        <v>569</v>
+      </c>
+      <c r="E100" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>289</v>
       </c>
@@ -4200,10 +4709,13 @@
         <v>290</v>
       </c>
       <c r="D101" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+        <v>570</v>
+      </c>
+      <c r="E101" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>291</v>
       </c>
@@ -4214,10 +4726,13 @@
         <v>68</v>
       </c>
       <c r="D102" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+        <v>571</v>
+      </c>
+      <c r="E102" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>292</v>
       </c>
@@ -4225,13 +4740,16 @@
         <v>0</v>
       </c>
       <c r="C103" t="s">
-        <v>758</v>
+        <v>742</v>
       </c>
       <c r="D103" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+        <v>572</v>
+      </c>
+      <c r="E103" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>293</v>
       </c>
@@ -4242,10 +4760,13 @@
         <v>165</v>
       </c>
       <c r="D104" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>573</v>
+      </c>
+      <c r="E104" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>294</v>
       </c>
@@ -4256,10 +4777,13 @@
         <v>52</v>
       </c>
       <c r="D105" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+      <c r="E105" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>295</v>
       </c>
@@ -4267,13 +4791,16 @@
         <v>0</v>
       </c>
       <c r="C106" t="s">
-        <v>759</v>
+        <v>743</v>
       </c>
       <c r="D106" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>575</v>
+      </c>
+      <c r="E106" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>296</v>
       </c>
@@ -4281,13 +4808,16 @@
         <v>0</v>
       </c>
       <c r="C107" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="D107" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+        <v>576</v>
+      </c>
+      <c r="E107" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>297</v>
       </c>
@@ -4298,10 +4828,13 @@
         <v>298</v>
       </c>
       <c r="D108" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+      <c r="E108" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>299</v>
       </c>
@@ -4312,10 +4845,13 @@
         <v>10</v>
       </c>
       <c r="D109" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+        <v>578</v>
+      </c>
+      <c r="E109" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>300</v>
       </c>
@@ -4326,10 +4862,13 @@
         <v>82</v>
       </c>
       <c r="D110" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+        <v>579</v>
+      </c>
+      <c r="E110" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>301</v>
       </c>
@@ -4340,10 +4879,13 @@
         <v>116</v>
       </c>
       <c r="D111" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+        <v>580</v>
+      </c>
+      <c r="E111" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>302</v>
       </c>
@@ -4354,10 +4896,13 @@
         <v>1</v>
       </c>
       <c r="D112" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+        <v>581</v>
+      </c>
+      <c r="E112" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>303</v>
       </c>
@@ -4368,10 +4913,13 @@
         <v>75</v>
       </c>
       <c r="D113" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+        <v>582</v>
+      </c>
+      <c r="E113" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>304</v>
       </c>
@@ -4382,10 +4930,13 @@
         <v>99</v>
       </c>
       <c r="D114" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+      <c r="E114" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>305</v>
       </c>
@@ -4396,10 +4947,13 @@
         <v>130</v>
       </c>
       <c r="D115" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+        <v>584</v>
+      </c>
+      <c r="E115" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>306</v>
       </c>
@@ -4410,10 +4964,13 @@
         <v>307</v>
       </c>
       <c r="D116" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+        <v>585</v>
+      </c>
+      <c r="E116" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>308</v>
       </c>
@@ -4424,10 +4981,13 @@
         <v>42</v>
       </c>
       <c r="D117" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+        <v>586</v>
+      </c>
+      <c r="E117" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>309</v>
       </c>
@@ -4438,10 +4998,13 @@
         <v>310</v>
       </c>
       <c r="D118" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+        <v>587</v>
+      </c>
+      <c r="E118" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>311</v>
       </c>
@@ -4452,10 +5015,13 @@
         <v>126</v>
       </c>
       <c r="D119" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+        <v>588</v>
+      </c>
+      <c r="E119" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>312</v>
       </c>
@@ -4466,10 +5032,13 @@
         <v>171</v>
       </c>
       <c r="D120" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+        <v>589</v>
+      </c>
+      <c r="E120" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>313</v>
       </c>
@@ -4480,10 +5049,13 @@
         <v>71</v>
       </c>
       <c r="D121" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+        <v>590</v>
+      </c>
+      <c r="E121" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>314</v>
       </c>
@@ -4494,10 +5066,13 @@
         <v>67</v>
       </c>
       <c r="D122" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+      <c r="E122" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>315</v>
       </c>
@@ -4505,13 +5080,16 @@
         <v>0</v>
       </c>
       <c r="C123" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="D123" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+        <v>592</v>
+      </c>
+      <c r="E123" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>316</v>
       </c>
@@ -4522,10 +5100,13 @@
         <v>29</v>
       </c>
       <c r="D124" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+      <c r="E124" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>317</v>
       </c>
@@ -4533,13 +5114,16 @@
         <v>0</v>
       </c>
       <c r="C125" t="s">
-        <v>762</v>
+        <v>746</v>
       </c>
       <c r="D125" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+        <v>594</v>
+      </c>
+      <c r="E125" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>318</v>
       </c>
@@ -4550,10 +5134,13 @@
         <v>76</v>
       </c>
       <c r="D126" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+        <v>595</v>
+      </c>
+      <c r="E126" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>319</v>
       </c>
@@ -4564,10 +5151,13 @@
         <v>83</v>
       </c>
       <c r="D127" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+        <v>596</v>
+      </c>
+      <c r="E127" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>320</v>
       </c>
@@ -4578,10 +5168,13 @@
         <v>122</v>
       </c>
       <c r="D128" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+        <v>597</v>
+      </c>
+      <c r="E128" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>321</v>
       </c>
@@ -4589,13 +5182,16 @@
         <v>0</v>
       </c>
       <c r="C129" t="s">
-        <v>763</v>
+        <v>747</v>
       </c>
       <c r="D129" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+        <v>598</v>
+      </c>
+      <c r="E129" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>322</v>
       </c>
@@ -4606,10 +5202,13 @@
         <v>323</v>
       </c>
       <c r="D130" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+        <v>599</v>
+      </c>
+      <c r="E130" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>324</v>
       </c>
@@ -4620,10 +5219,13 @@
         <v>39</v>
       </c>
       <c r="D131" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+      <c r="E131" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>325</v>
       </c>
@@ -4634,10 +5236,13 @@
         <v>21</v>
       </c>
       <c r="D132" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+        <v>601</v>
+      </c>
+      <c r="E132" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>326</v>
       </c>
@@ -4648,10 +5253,13 @@
         <v>155</v>
       </c>
       <c r="D133" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+      <c r="E133" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>327</v>
       </c>
@@ -4662,10 +5270,13 @@
         <v>158</v>
       </c>
       <c r="D134" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+        <v>603</v>
+      </c>
+      <c r="E134" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>328</v>
       </c>
@@ -4676,10 +5287,13 @@
         <v>168</v>
       </c>
       <c r="D135" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604</v>
+      </c>
+      <c r="E135" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>329</v>
       </c>
@@ -4690,10 +5304,13 @@
         <v>78</v>
       </c>
       <c r="D136" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+        <v>605</v>
+      </c>
+      <c r="E136" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>330</v>
       </c>
@@ -4704,10 +5321,13 @@
         <v>331</v>
       </c>
       <c r="D137" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+        <v>606</v>
+      </c>
+      <c r="E137" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>332</v>
       </c>
@@ -4718,10 +5338,13 @@
         <v>132</v>
       </c>
       <c r="D138" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+        <v>607</v>
+      </c>
+      <c r="E138" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>333</v>
       </c>
@@ -4732,10 +5355,13 @@
         <v>142</v>
       </c>
       <c r="D139" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+        <v>608</v>
+      </c>
+      <c r="E139" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>334</v>
       </c>
@@ -4746,10 +5372,13 @@
         <v>335</v>
       </c>
       <c r="D140" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+        <v>609</v>
+      </c>
+      <c r="E140" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>336</v>
       </c>
@@ -4760,10 +5389,13 @@
         <v>118</v>
       </c>
       <c r="D141" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+        <v>610</v>
+      </c>
+      <c r="E141" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>337</v>
       </c>
@@ -4774,10 +5406,13 @@
         <v>57</v>
       </c>
       <c r="D142" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+        <v>611</v>
+      </c>
+      <c r="E142" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>338</v>
       </c>
@@ -4788,10 +5423,13 @@
         <v>36</v>
       </c>
       <c r="D143" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+        <v>612</v>
+      </c>
+      <c r="E143" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>339</v>
       </c>
@@ -4802,10 +5440,13 @@
         <v>120</v>
       </c>
       <c r="D144" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+        <v>613</v>
+      </c>
+      <c r="E144" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>340</v>
       </c>
@@ -4816,10 +5457,13 @@
         <v>16</v>
       </c>
       <c r="D145" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+      <c r="E145" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>341</v>
       </c>
@@ -4830,10 +5474,13 @@
         <v>342</v>
       </c>
       <c r="D146" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+        <v>615</v>
+      </c>
+      <c r="E146" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>343</v>
       </c>
@@ -4844,10 +5491,13 @@
         <v>344</v>
       </c>
       <c r="D147" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+        <v>616</v>
+      </c>
+      <c r="E147" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>345</v>
       </c>
@@ -4855,13 +5505,16 @@
         <v>0</v>
       </c>
       <c r="C148" t="s">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="D148" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+        <v>617</v>
+      </c>
+      <c r="E148" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>346</v>
       </c>
@@ -4872,10 +5525,13 @@
         <v>128</v>
       </c>
       <c r="D149" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+      <c r="E149" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>347</v>
       </c>
@@ -4886,10 +5542,13 @@
         <v>348</v>
       </c>
       <c r="D150" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+      <c r="E150" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>349</v>
       </c>
@@ -4897,13 +5556,16 @@
         <v>0</v>
       </c>
       <c r="C151" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="D151" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+        <v>620</v>
+      </c>
+      <c r="E151" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>350</v>
       </c>
@@ -4914,10 +5576,13 @@
         <v>150</v>
       </c>
       <c r="D152" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+        <v>621</v>
+      </c>
+      <c r="E152" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>351</v>
       </c>
@@ -4928,10 +5593,13 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+        <v>622</v>
+      </c>
+      <c r="E153" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>352</v>
       </c>
@@ -4939,13 +5607,16 @@
         <v>0</v>
       </c>
       <c r="C154" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="D154" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+        <v>623</v>
+      </c>
+      <c r="E154" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>353</v>
       </c>
@@ -4956,10 +5627,13 @@
         <v>164</v>
       </c>
       <c r="D155" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+        <v>624</v>
+      </c>
+      <c r="E155" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>354</v>
       </c>
@@ -4970,10 +5644,13 @@
         <v>355</v>
       </c>
       <c r="D156" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+        <v>625</v>
+      </c>
+      <c r="E156" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>356</v>
       </c>
@@ -4984,10 +5661,13 @@
         <v>54</v>
       </c>
       <c r="D157" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="E157" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>357</v>
       </c>
@@ -4998,10 +5678,13 @@
         <v>117</v>
       </c>
       <c r="D158" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+      <c r="E158" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>358</v>
       </c>
@@ -5012,10 +5695,13 @@
         <v>359</v>
       </c>
       <c r="D159" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+      <c r="E159" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>360</v>
       </c>
@@ -5026,10 +5712,13 @@
         <v>60</v>
       </c>
       <c r="D160" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+        <v>629</v>
+      </c>
+      <c r="E160" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>361</v>
       </c>
@@ -5040,10 +5729,13 @@
         <v>362</v>
       </c>
       <c r="D161" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+        <v>630</v>
+      </c>
+      <c r="E161" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>363</v>
       </c>
@@ -5054,10 +5746,13 @@
         <v>108</v>
       </c>
       <c r="D162" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+        <v>631</v>
+      </c>
+      <c r="E162" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>364</v>
       </c>
@@ -5068,10 +5763,13 @@
         <v>112</v>
       </c>
       <c r="D163" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+        <v>632</v>
+      </c>
+      <c r="E163" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>365</v>
       </c>
@@ -5079,13 +5777,16 @@
         <v>0</v>
       </c>
       <c r="C164" t="s">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="D164" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+        <v>633</v>
+      </c>
+      <c r="E164" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>366</v>
       </c>
@@ -5093,13 +5794,16 @@
         <v>0</v>
       </c>
       <c r="C165" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="D165" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+        <v>634</v>
+      </c>
+      <c r="E165" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>367</v>
       </c>
@@ -5107,13 +5811,16 @@
         <v>0</v>
       </c>
       <c r="C166" t="s">
-        <v>769</v>
+        <v>753</v>
       </c>
       <c r="D166" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+        <v>635</v>
+      </c>
+      <c r="E166" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>368</v>
       </c>
@@ -5124,10 +5831,13 @@
         <v>26</v>
       </c>
       <c r="D167" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+      <c r="E167" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>369</v>
       </c>
@@ -5138,10 +5848,13 @@
         <v>93</v>
       </c>
       <c r="D168" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+        <v>637</v>
+      </c>
+      <c r="E168" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>370</v>
       </c>
@@ -5152,10 +5865,13 @@
         <v>147</v>
       </c>
       <c r="D169" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+        <v>638</v>
+      </c>
+      <c r="E169" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>371</v>
       </c>
@@ -5166,10 +5882,13 @@
         <v>135</v>
       </c>
       <c r="D170" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="E170" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>372</v>
       </c>
@@ -5177,13 +5896,16 @@
         <v>0</v>
       </c>
       <c r="C171" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="D171" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="E171" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>373</v>
       </c>
@@ -5194,10 +5916,13 @@
         <v>153</v>
       </c>
       <c r="D172" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="E172" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>374</v>
       </c>
@@ -5208,10 +5933,13 @@
         <v>105</v>
       </c>
       <c r="D173" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+      <c r="E173" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>375</v>
       </c>
@@ -5222,10 +5950,13 @@
         <v>119</v>
       </c>
       <c r="D174" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+        <v>643</v>
+      </c>
+      <c r="E174" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>376</v>
       </c>
@@ -5236,10 +5967,13 @@
         <v>377</v>
       </c>
       <c r="D175" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+        <v>644</v>
+      </c>
+      <c r="E175" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>378</v>
       </c>
@@ -5250,10 +5984,13 @@
         <v>127</v>
       </c>
       <c r="D176" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+        <v>645</v>
+      </c>
+      <c r="E176" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>379</v>
       </c>
@@ -5264,10 +6001,13 @@
         <v>115</v>
       </c>
       <c r="D177" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+        <v>646</v>
+      </c>
+      <c r="E177" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>380</v>
       </c>
@@ -5275,13 +6015,16 @@
         <v>0</v>
       </c>
       <c r="C178" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="D178" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+        <v>647</v>
+      </c>
+      <c r="E178" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>381</v>
       </c>
@@ -5292,10 +6035,13 @@
         <v>382</v>
       </c>
       <c r="D179" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+        <v>648</v>
+      </c>
+      <c r="E179" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>383</v>
       </c>
@@ -5306,10 +6052,13 @@
         <v>101</v>
       </c>
       <c r="D180" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+        <v>649</v>
+      </c>
+      <c r="E180" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>384</v>
       </c>
@@ -5320,10 +6069,13 @@
         <v>385</v>
       </c>
       <c r="D181" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+        <v>650</v>
+      </c>
+      <c r="E181" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>386</v>
       </c>
@@ -5334,10 +6086,13 @@
         <v>35</v>
       </c>
       <c r="D182" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+        <v>651</v>
+      </c>
+      <c r="E182" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>387</v>
       </c>
@@ -5348,10 +6103,13 @@
         <v>72</v>
       </c>
       <c r="D183" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+        <v>652</v>
+      </c>
+      <c r="E183" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>388</v>
       </c>
@@ -5362,10 +6120,13 @@
         <v>175</v>
       </c>
       <c r="D184" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E184" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>389</v>
       </c>
@@ -5376,10 +6137,13 @@
         <v>167</v>
       </c>
       <c r="D185" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+      <c r="E185" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>390</v>
       </c>
@@ -5390,10 +6154,13 @@
         <v>56</v>
       </c>
       <c r="D186" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+      <c r="E186" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>391</v>
       </c>
@@ -5404,10 +6171,13 @@
         <v>14</v>
       </c>
       <c r="D187" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+        <v>656</v>
+      </c>
+      <c r="E187" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>392</v>
       </c>
@@ -5415,13 +6185,16 @@
         <v>0</v>
       </c>
       <c r="C188" t="s">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="D188" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+        <v>657</v>
+      </c>
+      <c r="E188" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>393</v>
       </c>
@@ -5432,10 +6205,13 @@
         <v>88</v>
       </c>
       <c r="D189" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+        <v>658</v>
+      </c>
+      <c r="E189" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>394</v>
       </c>
@@ -5446,10 +6222,13 @@
         <v>94</v>
       </c>
       <c r="D190" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+        <v>659</v>
+      </c>
+      <c r="E190" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>395</v>
       </c>
@@ -5460,10 +6239,13 @@
         <v>37</v>
       </c>
       <c r="D191" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+        <v>660</v>
+      </c>
+      <c r="E191" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>396</v>
       </c>
@@ -5474,10 +6256,13 @@
         <v>397</v>
       </c>
       <c r="D192" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+        <v>661</v>
+      </c>
+      <c r="E192" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>398</v>
       </c>
@@ -5488,10 +6273,13 @@
         <v>110</v>
       </c>
       <c r="D193" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+        <v>662</v>
+      </c>
+      <c r="E193" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>399</v>
       </c>
@@ -5502,10 +6290,13 @@
         <v>91</v>
       </c>
       <c r="D194" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+        <v>663</v>
+      </c>
+      <c r="E194" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>400</v>
       </c>
@@ -5516,10 +6307,13 @@
         <v>401</v>
       </c>
       <c r="D195" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+        <v>664</v>
+      </c>
+      <c r="E195" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>402</v>
       </c>
@@ -5530,10 +6324,13 @@
         <v>136</v>
       </c>
       <c r="D196" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+        <v>665</v>
+      </c>
+      <c r="E196" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>403</v>
       </c>
@@ -5544,10 +6341,13 @@
         <v>146</v>
       </c>
       <c r="D197" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+        <v>666</v>
+      </c>
+      <c r="E197" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>404</v>
       </c>
@@ -5558,10 +6358,13 @@
         <v>173</v>
       </c>
       <c r="D198" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+        <v>667</v>
+      </c>
+      <c r="E198" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>405</v>
       </c>
@@ -5572,10 +6375,13 @@
         <v>141</v>
       </c>
       <c r="D199" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+        <v>668</v>
+      </c>
+      <c r="E199" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>406</v>
       </c>
@@ -5586,10 +6392,13 @@
         <v>137</v>
       </c>
       <c r="D200" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+        <v>669</v>
+      </c>
+      <c r="E200" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>407</v>
       </c>
@@ -5600,10 +6409,13 @@
         <v>92</v>
       </c>
       <c r="D201" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+        <v>670</v>
+      </c>
+      <c r="E201" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>408</v>
       </c>
@@ -5614,10 +6426,13 @@
         <v>53</v>
       </c>
       <c r="D202" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+        <v>671</v>
+      </c>
+      <c r="E202" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>409</v>
       </c>
@@ -5628,10 +6443,13 @@
         <v>3</v>
       </c>
       <c r="D203" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+        <v>672</v>
+      </c>
+      <c r="E203" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>410</v>
       </c>
@@ -5642,10 +6460,13 @@
         <v>47</v>
       </c>
       <c r="D204" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+        <v>673</v>
+      </c>
+      <c r="E204" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>411</v>
       </c>
@@ -5656,10 +6477,13 @@
         <v>134</v>
       </c>
       <c r="D205" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+        <v>674</v>
+      </c>
+      <c r="E205" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>412</v>
       </c>
@@ -5667,13 +6491,16 @@
         <v>0</v>
       </c>
       <c r="C206" t="s">
-        <v>773</v>
+        <v>757</v>
       </c>
       <c r="D206" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+        <v>675</v>
+      </c>
+      <c r="E206" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>413</v>
       </c>
@@ -5684,10 +6511,13 @@
         <v>79</v>
       </c>
       <c r="D207" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+        <v>676</v>
+      </c>
+      <c r="E207" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>414</v>
       </c>
@@ -5698,10 +6528,13 @@
         <v>61</v>
       </c>
       <c r="D208" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+        <v>677</v>
+      </c>
+      <c r="E208" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>415</v>
       </c>
@@ -5712,10 +6545,13 @@
         <v>69</v>
       </c>
       <c r="D209" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+        <v>678</v>
+      </c>
+      <c r="E209" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>416</v>
       </c>
@@ -5723,13 +6559,16 @@
         <v>0</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>774</v>
+        <v>758</v>
       </c>
       <c r="D210" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+        <v>679</v>
+      </c>
+      <c r="E210" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>417</v>
       </c>
@@ -5740,10 +6579,13 @@
         <v>50</v>
       </c>
       <c r="D211" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+        <v>680</v>
+      </c>
+      <c r="E211" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>418</v>
       </c>
@@ -5754,10 +6596,13 @@
         <v>44</v>
       </c>
       <c r="D212" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+        <v>680</v>
+      </c>
+      <c r="E212" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>419</v>
       </c>
@@ -5768,10 +6613,13 @@
         <v>27</v>
       </c>
       <c r="D213" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+        <v>681</v>
+      </c>
+      <c r="E213" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>420</v>
       </c>
@@ -5782,10 +6630,13 @@
         <v>125</v>
       </c>
       <c r="D214" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+        <v>682</v>
+      </c>
+      <c r="E214" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>421</v>
       </c>
@@ -5793,13 +6644,16 @@
         <v>0</v>
       </c>
       <c r="C215" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="D215" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+        <v>683</v>
+      </c>
+      <c r="E215" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>422</v>
       </c>
@@ -5810,10 +6664,13 @@
         <v>45</v>
       </c>
       <c r="D216" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+        <v>684</v>
+      </c>
+      <c r="E216" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>423</v>
       </c>
@@ -5824,10 +6681,13 @@
         <v>77</v>
       </c>
       <c r="D217" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+        <v>685</v>
+      </c>
+      <c r="E217" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>424</v>
       </c>
@@ -5838,10 +6698,13 @@
         <v>86</v>
       </c>
       <c r="D218" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+        <v>686</v>
+      </c>
+      <c r="E218" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>425</v>
       </c>
@@ -5849,13 +6712,16 @@
         <v>0</v>
       </c>
       <c r="C219" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="D219" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+        <v>687</v>
+      </c>
+      <c r="E219" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>426</v>
       </c>
@@ -5866,10 +6732,13 @@
         <v>22</v>
       </c>
       <c r="D220" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+        <v>688</v>
+      </c>
+      <c r="E220" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>427</v>
       </c>
@@ -5880,10 +6749,13 @@
         <v>24</v>
       </c>
       <c r="D221" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+        <v>689</v>
+      </c>
+      <c r="E221" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>428</v>
       </c>
@@ -5894,10 +6766,13 @@
         <v>162</v>
       </c>
       <c r="D222" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+        <v>690</v>
+      </c>
+      <c r="E222" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>429</v>
       </c>
@@ -5908,10 +6783,13 @@
         <v>169</v>
       </c>
       <c r="D223" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+        <v>691</v>
+      </c>
+      <c r="E223" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>430</v>
       </c>
@@ -5922,10 +6800,13 @@
         <v>156</v>
       </c>
       <c r="D224" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+        <v>692</v>
+      </c>
+      <c r="E224" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>431</v>
       </c>
@@ -5936,10 +6817,13 @@
         <v>107</v>
       </c>
       <c r="D225" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+      <c r="E225" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>432</v>
       </c>
@@ -5950,10 +6834,13 @@
         <v>433</v>
       </c>
       <c r="D226" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+      <c r="E226" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>434</v>
       </c>
@@ -5961,13 +6848,16 @@
         <v>0</v>
       </c>
       <c r="C227" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="D227" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+        <v>695</v>
+      </c>
+      <c r="E227" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>435</v>
       </c>
@@ -5975,13 +6865,16 @@
         <v>0</v>
       </c>
       <c r="C228" t="s">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="D228" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+        <v>696</v>
+      </c>
+      <c r="E228" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>436</v>
       </c>
@@ -5989,13 +6882,16 @@
         <v>0</v>
       </c>
       <c r="C229" t="s">
-        <v>779</v>
+        <v>763</v>
       </c>
       <c r="D229" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+        <v>697</v>
+      </c>
+      <c r="E229" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>437</v>
       </c>
@@ -6006,10 +6902,13 @@
         <v>102</v>
       </c>
       <c r="D230" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+        <v>698</v>
+      </c>
+      <c r="E230" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>438</v>
       </c>
@@ -6020,10 +6919,13 @@
         <v>111</v>
       </c>
       <c r="D231" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+      <c r="E231" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>439</v>
       </c>
@@ -6031,13 +6933,16 @@
         <v>0</v>
       </c>
       <c r="C232" t="s">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="D232" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+        <v>700</v>
+      </c>
+      <c r="E232" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>440</v>
       </c>
@@ -6048,10 +6953,13 @@
         <v>441</v>
       </c>
       <c r="D233" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+        <v>701</v>
+      </c>
+      <c r="E233" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>442</v>
       </c>
@@ -6062,10 +6970,13 @@
         <v>17</v>
       </c>
       <c r="D234" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+        <v>702</v>
+      </c>
+      <c r="E234" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>443</v>
       </c>
@@ -6076,10 +6987,13 @@
         <v>95</v>
       </c>
       <c r="D235" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+      <c r="E235" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>444</v>
       </c>
@@ -6090,10 +7004,13 @@
         <v>51</v>
       </c>
       <c r="D236" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+        <v>704</v>
+      </c>
+      <c r="E236" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>445</v>
       </c>
@@ -6104,10 +7021,13 @@
         <v>139</v>
       </c>
       <c r="D237" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+        <v>705</v>
+      </c>
+      <c r="E237" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>446</v>
       </c>
@@ -6115,13 +7035,16 @@
         <v>0</v>
       </c>
       <c r="C238" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="D238" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+        <v>706</v>
+      </c>
+      <c r="E238" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>447</v>
       </c>
@@ -6132,10 +7055,13 @@
         <v>33</v>
       </c>
       <c r="D239" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+        <v>707</v>
+      </c>
+      <c r="E239" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>448</v>
       </c>
@@ -6146,10 +7072,13 @@
         <v>34</v>
       </c>
       <c r="D240" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+        <v>708</v>
+      </c>
+      <c r="E240" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>449</v>
       </c>
@@ -6160,10 +7089,13 @@
         <v>12</v>
       </c>
       <c r="D241" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+        <v>709</v>
+      </c>
+      <c r="E241" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>450</v>
       </c>
@@ -6174,10 +7106,13 @@
         <v>7</v>
       </c>
       <c r="D242" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+        <v>710</v>
+      </c>
+      <c r="E242" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>451</v>
       </c>
@@ -6188,10 +7123,13 @@
         <v>8</v>
       </c>
       <c r="D243" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+      <c r="E243" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>452</v>
       </c>
@@ -6202,10 +7140,13 @@
         <v>70</v>
       </c>
       <c r="D244" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+        <v>711</v>
+      </c>
+      <c r="E244" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>453</v>
       </c>
@@ -6213,13 +7154,16 @@
         <v>80</v>
       </c>
       <c r="C245" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="D245" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+        <v>712</v>
+      </c>
+      <c r="E245" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>454</v>
       </c>
@@ -6227,13 +7171,16 @@
         <v>80</v>
       </c>
       <c r="C246" t="s">
-        <v>783</v>
+        <v>767</v>
       </c>
       <c r="D246" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+        <v>713</v>
+      </c>
+      <c r="E246" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>455</v>
       </c>
@@ -6244,10 +7191,13 @@
         <v>66</v>
       </c>
       <c r="D247" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+        <v>714</v>
+      </c>
+      <c r="E247" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>456</v>
       </c>
@@ -6258,10 +7208,13 @@
         <v>55</v>
       </c>
       <c r="D248" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+        <v>715</v>
+      </c>
+      <c r="E248" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>457</v>
       </c>
@@ -6272,10 +7225,13 @@
         <v>62</v>
       </c>
       <c r="D249" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+        <v>716</v>
+      </c>
+      <c r="E249" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>458</v>
       </c>
@@ -6286,10 +7242,13 @@
         <v>19</v>
       </c>
       <c r="D250" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+        <v>717</v>
+      </c>
+      <c r="E250" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>459</v>
       </c>
@@ -6297,13 +7256,16 @@
         <v>80</v>
       </c>
       <c r="C251" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="D251" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+        <v>720</v>
+      </c>
+      <c r="E251" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>460</v>
       </c>
@@ -6311,13 +7273,16 @@
         <v>80</v>
       </c>
       <c r="C252" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="D252" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+        <v>721</v>
+      </c>
+      <c r="E252" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>461</v>
       </c>
@@ -6328,10 +7293,13 @@
         <v>462</v>
       </c>
       <c r="D253" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="E253" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>463</v>
       </c>
@@ -6339,13 +7307,16 @@
         <v>80</v>
       </c>
       <c r="C254" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="D254" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+      <c r="E254" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>464</v>
       </c>
@@ -6353,13 +7324,16 @@
         <v>80</v>
       </c>
       <c r="C255" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="D255" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+      <c r="E255" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>465</v>
       </c>
@@ -6370,10 +7344,13 @@
         <v>466</v>
       </c>
       <c r="D256" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+      <c r="E256" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>467</v>
       </c>
@@ -6384,2842 +7361,14 @@
         <v>468</v>
       </c>
       <c r="D257" t="s">
-        <v>742</v>
+        <v>726</v>
+      </c>
+      <c r="E257" t="e">
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D552" xr:uid="{EB689665-45D9-42F4-AA4C-1FD1A1AE5053}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052F7F2D-15F0-4A25-9EAD-48B1846BD2E4}">
-  <dimension ref="A1:C256"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="47" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B1" t="s">
-        <v>471</v>
-      </c>
-      <c r="C1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B3" t="s">
-        <v>473</v>
-      </c>
-      <c r="C3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>726</v>
-      </c>
-      <c r="B4" t="s">
-        <v>474</v>
-      </c>
-      <c r="C4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B5" t="s">
-        <v>475</v>
-      </c>
-      <c r="C5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B6" t="s">
-        <v>476</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B7" t="s">
-        <v>477</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>185</v>
-      </c>
-      <c r="B8" t="s">
-        <v>478</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>186</v>
-      </c>
-      <c r="B9" t="s">
-        <v>479</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>187</v>
-      </c>
-      <c r="B10" t="s">
-        <v>480</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>188</v>
-      </c>
-      <c r="B11" t="s">
-        <v>481</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B12" t="s">
-        <v>482</v>
-      </c>
-      <c r="C12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>191</v>
-      </c>
-      <c r="B13" t="s">
-        <v>483</v>
-      </c>
-      <c r="C13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>192</v>
-      </c>
-      <c r="B14" t="s">
-        <v>484</v>
-      </c>
-      <c r="C14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>193</v>
-      </c>
-      <c r="B15" t="s">
-        <v>485</v>
-      </c>
-      <c r="C15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>194</v>
-      </c>
-      <c r="B16" t="s">
-        <v>486</v>
-      </c>
-      <c r="C16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>195</v>
-      </c>
-      <c r="B17" t="s">
-        <v>487</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>197</v>
-      </c>
-      <c r="B18" t="s">
-        <v>488</v>
-      </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>198</v>
-      </c>
-      <c r="B19" t="s">
-        <v>489</v>
-      </c>
-      <c r="C19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>199</v>
-      </c>
-      <c r="B20" t="s">
-        <v>490</v>
-      </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>200</v>
-      </c>
-      <c r="B21" t="s">
-        <v>491</v>
-      </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>202</v>
-      </c>
-      <c r="B22" t="s">
-        <v>492</v>
-      </c>
-      <c r="C22" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>203</v>
-      </c>
-      <c r="B23" t="s">
-        <v>493</v>
-      </c>
-      <c r="C23" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>204</v>
-      </c>
-      <c r="B24" t="s">
-        <v>494</v>
-      </c>
-      <c r="C24" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>205</v>
-      </c>
-      <c r="B25" t="s">
-        <v>495</v>
-      </c>
-      <c r="C25" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>206</v>
-      </c>
-      <c r="B26" t="s">
-        <v>496</v>
-      </c>
-      <c r="C26" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>207</v>
-      </c>
-      <c r="B27" t="s">
-        <v>497</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>208</v>
-      </c>
-      <c r="B28" t="s">
-        <v>498</v>
-      </c>
-      <c r="C28" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>209</v>
-      </c>
-      <c r="B29" t="s">
-        <v>499</v>
-      </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>210</v>
-      </c>
-      <c r="B30" t="s">
-        <v>500</v>
-      </c>
-      <c r="C30" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>211</v>
-      </c>
-      <c r="B31" t="s">
-        <v>501</v>
-      </c>
-      <c r="C31" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>212</v>
-      </c>
-      <c r="B32" t="s">
-        <v>502</v>
-      </c>
-      <c r="C32" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>213</v>
-      </c>
-      <c r="B33" t="s">
-        <v>503</v>
-      </c>
-      <c r="C33" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>214</v>
-      </c>
-      <c r="B34" t="s">
-        <v>504</v>
-      </c>
-      <c r="C34" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>216</v>
-      </c>
-      <c r="B35" t="s">
-        <v>505</v>
-      </c>
-      <c r="C35" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>217</v>
-      </c>
-      <c r="B36" t="s">
-        <v>506</v>
-      </c>
-      <c r="C36" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>218</v>
-      </c>
-      <c r="B37" t="s">
-        <v>507</v>
-      </c>
-      <c r="C37" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>727</v>
-      </c>
-      <c r="B38" t="s">
-        <v>508</v>
-      </c>
-      <c r="C38" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>220</v>
-      </c>
-      <c r="B39" t="s">
-        <v>509</v>
-      </c>
-      <c r="C39" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>221</v>
-      </c>
-      <c r="B40" t="s">
-        <v>510</v>
-      </c>
-      <c r="C40" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>222</v>
-      </c>
-      <c r="B41" t="s">
-        <v>511</v>
-      </c>
-      <c r="C41" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>223</v>
-      </c>
-      <c r="B42" t="s">
-        <v>512</v>
-      </c>
-      <c r="C42" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>224</v>
-      </c>
-      <c r="B43" t="s">
-        <v>513</v>
-      </c>
-      <c r="C43" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>225</v>
-      </c>
-      <c r="B44" t="s">
-        <v>514</v>
-      </c>
-      <c r="C44" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>226</v>
-      </c>
-      <c r="B45" t="s">
-        <v>515</v>
-      </c>
-      <c r="C45" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>227</v>
-      </c>
-      <c r="B46" t="s">
-        <v>516</v>
-      </c>
-      <c r="C46" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>228</v>
-      </c>
-      <c r="B47" t="s">
-        <v>517</v>
-      </c>
-      <c r="C47" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>229</v>
-      </c>
-      <c r="B48" t="s">
-        <v>518</v>
-      </c>
-      <c r="C48" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>230</v>
-      </c>
-      <c r="B49" t="s">
-        <v>519</v>
-      </c>
-      <c r="C49" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>231</v>
-      </c>
-      <c r="B50" t="s">
-        <v>520</v>
-      </c>
-      <c r="C50" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>232</v>
-      </c>
-      <c r="B51" t="s">
-        <v>521</v>
-      </c>
-      <c r="C51" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>233</v>
-      </c>
-      <c r="B52" t="s">
-        <v>522</v>
-      </c>
-      <c r="C52" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>234</v>
-      </c>
-      <c r="B53" t="s">
-        <v>523</v>
-      </c>
-      <c r="C53" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>728</v>
-      </c>
-      <c r="B54" t="s">
-        <v>524</v>
-      </c>
-      <c r="C54" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>235</v>
-      </c>
-      <c r="B55" t="s">
-        <v>525</v>
-      </c>
-      <c r="C55" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>236</v>
-      </c>
-      <c r="B56" t="s">
-        <v>526</v>
-      </c>
-      <c r="C56" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>237</v>
-      </c>
-      <c r="B57" t="s">
-        <v>527</v>
-      </c>
-      <c r="C57" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>238</v>
-      </c>
-      <c r="B58" t="s">
-        <v>528</v>
-      </c>
-      <c r="C58" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>239</v>
-      </c>
-      <c r="B59" t="s">
-        <v>529</v>
-      </c>
-      <c r="C59" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>240</v>
-      </c>
-      <c r="B60" t="s">
-        <v>530</v>
-      </c>
-      <c r="C60" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>241</v>
-      </c>
-      <c r="B61" t="s">
-        <v>531</v>
-      </c>
-      <c r="C61" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>242</v>
-      </c>
-      <c r="B62" t="s">
-        <v>532</v>
-      </c>
-      <c r="C62" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>243</v>
-      </c>
-      <c r="B63" t="s">
-        <v>533</v>
-      </c>
-      <c r="C63" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>244</v>
-      </c>
-      <c r="B64" t="s">
-        <v>534</v>
-      </c>
-      <c r="C64" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>245</v>
-      </c>
-      <c r="B65" t="s">
-        <v>535</v>
-      </c>
-      <c r="C65" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>246</v>
-      </c>
-      <c r="B66" t="s">
-        <v>536</v>
-      </c>
-      <c r="C66" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>248</v>
-      </c>
-      <c r="B67" t="s">
-        <v>537</v>
-      </c>
-      <c r="C67" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>249</v>
-      </c>
-      <c r="B68" t="s">
-        <v>538</v>
-      </c>
-      <c r="C68" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>250</v>
-      </c>
-      <c r="B69" t="s">
-        <v>539</v>
-      </c>
-      <c r="C69" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>251</v>
-      </c>
-      <c r="B70" t="s">
-        <v>540</v>
-      </c>
-      <c r="C70" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>252</v>
-      </c>
-      <c r="B71" t="s">
-        <v>541</v>
-      </c>
-      <c r="C71" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>253</v>
-      </c>
-      <c r="B72" t="s">
-        <v>542</v>
-      </c>
-      <c r="C72" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>254</v>
-      </c>
-      <c r="B73" t="s">
-        <v>543</v>
-      </c>
-      <c r="C73" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>255</v>
-      </c>
-      <c r="B74" t="s">
-        <v>544</v>
-      </c>
-      <c r="C74" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>257</v>
-      </c>
-      <c r="B75" t="s">
-        <v>545</v>
-      </c>
-      <c r="C75" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>258</v>
-      </c>
-      <c r="B76" t="s">
-        <v>546</v>
-      </c>
-      <c r="C76" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>259</v>
-      </c>
-      <c r="B77" t="s">
-        <v>547</v>
-      </c>
-      <c r="C77" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>260</v>
-      </c>
-      <c r="B78" t="s">
-        <v>548</v>
-      </c>
-      <c r="C78" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>261</v>
-      </c>
-      <c r="B79" t="s">
-        <v>549</v>
-      </c>
-      <c r="C79" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>262</v>
-      </c>
-      <c r="B80" t="s">
-        <v>550</v>
-      </c>
-      <c r="C80" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>263</v>
-      </c>
-      <c r="B81" t="s">
-        <v>551</v>
-      </c>
-      <c r="C81" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>264</v>
-      </c>
-      <c r="B82" t="s">
-        <v>552</v>
-      </c>
-      <c r="C82" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>265</v>
-      </c>
-      <c r="B83" t="s">
-        <v>553</v>
-      </c>
-      <c r="C83" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>266</v>
-      </c>
-      <c r="B84" t="s">
-        <v>554</v>
-      </c>
-      <c r="C84" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>267</v>
-      </c>
-      <c r="B85" t="s">
-        <v>555</v>
-      </c>
-      <c r="C85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>268</v>
-      </c>
-      <c r="B86" t="s">
-        <v>556</v>
-      </c>
-      <c r="C86" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>270</v>
-      </c>
-      <c r="B87" t="s">
-        <v>557</v>
-      </c>
-      <c r="C87" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>271</v>
-      </c>
-      <c r="B88" t="s">
-        <v>558</v>
-      </c>
-      <c r="C88" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>272</v>
-      </c>
-      <c r="B89" t="s">
-        <v>559</v>
-      </c>
-      <c r="C89" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>273</v>
-      </c>
-      <c r="B90" t="s">
-        <v>560</v>
-      </c>
-      <c r="C90" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>274</v>
-      </c>
-      <c r="B91" t="s">
-        <v>561</v>
-      </c>
-      <c r="C91" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>275</v>
-      </c>
-      <c r="B92" t="s">
-        <v>562</v>
-      </c>
-      <c r="C92" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>276</v>
-      </c>
-      <c r="B93" t="s">
-        <v>563</v>
-      </c>
-      <c r="C93" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>277</v>
-      </c>
-      <c r="B94" t="s">
-        <v>564</v>
-      </c>
-      <c r="C94" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>278</v>
-      </c>
-      <c r="B95" t="s">
-        <v>565</v>
-      </c>
-      <c r="C95" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>280</v>
-      </c>
-      <c r="B96" t="s">
-        <v>566</v>
-      </c>
-      <c r="C96" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>281</v>
-      </c>
-      <c r="B97" t="s">
-        <v>567</v>
-      </c>
-      <c r="C97" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>282</v>
-      </c>
-      <c r="B98" t="s">
-        <v>568</v>
-      </c>
-      <c r="C98" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>283</v>
-      </c>
-      <c r="B99" t="s">
-        <v>569</v>
-      </c>
-      <c r="C99" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>285</v>
-      </c>
-      <c r="B100" t="s">
-        <v>570</v>
-      </c>
-      <c r="C100" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>286</v>
-      </c>
-      <c r="B101" t="s">
-        <v>571</v>
-      </c>
-      <c r="C101" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>287</v>
-      </c>
-      <c r="B102" t="s">
-        <v>572</v>
-      </c>
-      <c r="C102" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>289</v>
-      </c>
-      <c r="B103" t="s">
-        <v>573</v>
-      </c>
-      <c r="C103" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>291</v>
-      </c>
-      <c r="B104" t="s">
-        <v>574</v>
-      </c>
-      <c r="C104" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>292</v>
-      </c>
-      <c r="B105" t="s">
-        <v>575</v>
-      </c>
-      <c r="C105" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>293</v>
-      </c>
-      <c r="B106" t="s">
-        <v>576</v>
-      </c>
-      <c r="C106" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>294</v>
-      </c>
-      <c r="B107" t="s">
-        <v>577</v>
-      </c>
-      <c r="C107" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>295</v>
-      </c>
-      <c r="B108" t="s">
-        <v>578</v>
-      </c>
-      <c r="C108" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>296</v>
-      </c>
-      <c r="B109" t="s">
-        <v>579</v>
-      </c>
-      <c r="C109" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>297</v>
-      </c>
-      <c r="B110" t="s">
-        <v>580</v>
-      </c>
-      <c r="C110" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>299</v>
-      </c>
-      <c r="B111" t="s">
-        <v>581</v>
-      </c>
-      <c r="C111" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>300</v>
-      </c>
-      <c r="B112" t="s">
-        <v>582</v>
-      </c>
-      <c r="C112" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>301</v>
-      </c>
-      <c r="B113" t="s">
-        <v>583</v>
-      </c>
-      <c r="C113" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>302</v>
-      </c>
-      <c r="B114" t="s">
-        <v>584</v>
-      </c>
-      <c r="C114" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>303</v>
-      </c>
-      <c r="B115" t="s">
-        <v>585</v>
-      </c>
-      <c r="C115" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>304</v>
-      </c>
-      <c r="B116" t="s">
-        <v>586</v>
-      </c>
-      <c r="C116" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>305</v>
-      </c>
-      <c r="B117" t="s">
-        <v>587</v>
-      </c>
-      <c r="C117" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>306</v>
-      </c>
-      <c r="B118" t="s">
-        <v>588</v>
-      </c>
-      <c r="C118" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>308</v>
-      </c>
-      <c r="B119" t="s">
-        <v>589</v>
-      </c>
-      <c r="C119" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>309</v>
-      </c>
-      <c r="B120" t="s">
-        <v>590</v>
-      </c>
-      <c r="C120" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>311</v>
-      </c>
-      <c r="B121" t="s">
-        <v>591</v>
-      </c>
-      <c r="C121" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>312</v>
-      </c>
-      <c r="B122" t="s">
-        <v>592</v>
-      </c>
-      <c r="C122" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>313</v>
-      </c>
-      <c r="B123" t="s">
-        <v>593</v>
-      </c>
-      <c r="C123" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>314</v>
-      </c>
-      <c r="B124" t="s">
-        <v>594</v>
-      </c>
-      <c r="C124" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>315</v>
-      </c>
-      <c r="B125" t="s">
-        <v>595</v>
-      </c>
-      <c r="C125" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>316</v>
-      </c>
-      <c r="B126" t="s">
-        <v>596</v>
-      </c>
-      <c r="C126" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>317</v>
-      </c>
-      <c r="B127" t="s">
-        <v>597</v>
-      </c>
-      <c r="C127" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>318</v>
-      </c>
-      <c r="B128" t="s">
-        <v>598</v>
-      </c>
-      <c r="C128" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>319</v>
-      </c>
-      <c r="B129" t="s">
-        <v>599</v>
-      </c>
-      <c r="C129" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>729</v>
-      </c>
-      <c r="B130" t="s">
-        <v>600</v>
-      </c>
-      <c r="C130" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>320</v>
-      </c>
-      <c r="B131" t="s">
-        <v>601</v>
-      </c>
-      <c r="C131" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>321</v>
-      </c>
-      <c r="B132" t="s">
-        <v>602</v>
-      </c>
-      <c r="C132" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>322</v>
-      </c>
-      <c r="B133" t="s">
-        <v>603</v>
-      </c>
-      <c r="C133" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>324</v>
-      </c>
-      <c r="B134" t="s">
-        <v>604</v>
-      </c>
-      <c r="C134" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>325</v>
-      </c>
-      <c r="B135" t="s">
-        <v>605</v>
-      </c>
-      <c r="C135" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>326</v>
-      </c>
-      <c r="B136" t="s">
-        <v>606</v>
-      </c>
-      <c r="C136" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>327</v>
-      </c>
-      <c r="B137" t="s">
-        <v>607</v>
-      </c>
-      <c r="C137" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>328</v>
-      </c>
-      <c r="B138" t="s">
-        <v>608</v>
-      </c>
-      <c r="C138" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>329</v>
-      </c>
-      <c r="B139" t="s">
-        <v>609</v>
-      </c>
-      <c r="C139" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>330</v>
-      </c>
-      <c r="B140" t="s">
-        <v>610</v>
-      </c>
-      <c r="C140" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>332</v>
-      </c>
-      <c r="B141" t="s">
-        <v>611</v>
-      </c>
-      <c r="C141" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>333</v>
-      </c>
-      <c r="B142" t="s">
-        <v>612</v>
-      </c>
-      <c r="C142" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>334</v>
-      </c>
-      <c r="B143" t="s">
-        <v>613</v>
-      </c>
-      <c r="C143" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>336</v>
-      </c>
-      <c r="B144" t="s">
-        <v>614</v>
-      </c>
-      <c r="C144" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>337</v>
-      </c>
-      <c r="B145" t="s">
-        <v>615</v>
-      </c>
-      <c r="C145" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>338</v>
-      </c>
-      <c r="B146" t="s">
-        <v>616</v>
-      </c>
-      <c r="C146" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>339</v>
-      </c>
-      <c r="B147" t="s">
-        <v>617</v>
-      </c>
-      <c r="C147" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>340</v>
-      </c>
-      <c r="B148" t="s">
-        <v>618</v>
-      </c>
-      <c r="C148" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>341</v>
-      </c>
-      <c r="B149" t="s">
-        <v>619</v>
-      </c>
-      <c r="C149" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>343</v>
-      </c>
-      <c r="B150" t="s">
-        <v>620</v>
-      </c>
-      <c r="C150" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>345</v>
-      </c>
-      <c r="B151" t="s">
-        <v>621</v>
-      </c>
-      <c r="C151" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>346</v>
-      </c>
-      <c r="B152" t="s">
-        <v>622</v>
-      </c>
-      <c r="C152" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>347</v>
-      </c>
-      <c r="B153" t="s">
-        <v>623</v>
-      </c>
-      <c r="C153" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>730</v>
-      </c>
-      <c r="B154" t="s">
-        <v>624</v>
-      </c>
-      <c r="C154" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>349</v>
-      </c>
-      <c r="B155" t="s">
-        <v>625</v>
-      </c>
-      <c r="C155" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>350</v>
-      </c>
-      <c r="B156" t="s">
-        <v>626</v>
-      </c>
-      <c r="C156" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>351</v>
-      </c>
-      <c r="B157" t="s">
-        <v>627</v>
-      </c>
-      <c r="C157" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>352</v>
-      </c>
-      <c r="B158" t="s">
-        <v>628</v>
-      </c>
-      <c r="C158" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>353</v>
-      </c>
-      <c r="B159" t="s">
-        <v>629</v>
-      </c>
-      <c r="C159" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>354</v>
-      </c>
-      <c r="B160" t="s">
-        <v>630</v>
-      </c>
-      <c r="C160" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>356</v>
-      </c>
-      <c r="B161" t="s">
-        <v>631</v>
-      </c>
-      <c r="C161" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>357</v>
-      </c>
-      <c r="B162" t="s">
-        <v>632</v>
-      </c>
-      <c r="C162" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>358</v>
-      </c>
-      <c r="B163" t="s">
-        <v>633</v>
-      </c>
-      <c r="C163" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>360</v>
-      </c>
-      <c r="B164" t="s">
-        <v>634</v>
-      </c>
-      <c r="C164" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>361</v>
-      </c>
-      <c r="B165" t="s">
-        <v>635</v>
-      </c>
-      <c r="C165" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>363</v>
-      </c>
-      <c r="B166" t="s">
-        <v>636</v>
-      </c>
-      <c r="C166" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>364</v>
-      </c>
-      <c r="B167" t="s">
-        <v>637</v>
-      </c>
-      <c r="C167" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>365</v>
-      </c>
-      <c r="B168" t="s">
-        <v>638</v>
-      </c>
-      <c r="C168" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>366</v>
-      </c>
-      <c r="B169" t="s">
-        <v>639</v>
-      </c>
-      <c r="C169" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>367</v>
-      </c>
-      <c r="B170" t="s">
-        <v>640</v>
-      </c>
-      <c r="C170" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>368</v>
-      </c>
-      <c r="B171" t="s">
-        <v>641</v>
-      </c>
-      <c r="C171" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>369</v>
-      </c>
-      <c r="B172" t="s">
-        <v>642</v>
-      </c>
-      <c r="C172" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>370</v>
-      </c>
-      <c r="B173" t="s">
-        <v>643</v>
-      </c>
-      <c r="C173" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>371</v>
-      </c>
-      <c r="B174" t="s">
-        <v>644</v>
-      </c>
-      <c r="C174" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>372</v>
-      </c>
-      <c r="B175" t="s">
-        <v>645</v>
-      </c>
-      <c r="C175" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>373</v>
-      </c>
-      <c r="B176" t="s">
-        <v>646</v>
-      </c>
-      <c r="C176" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>374</v>
-      </c>
-      <c r="B177" t="s">
-        <v>647</v>
-      </c>
-      <c r="C177" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>375</v>
-      </c>
-      <c r="B178" t="s">
-        <v>648</v>
-      </c>
-      <c r="C178" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>376</v>
-      </c>
-      <c r="B179" t="s">
-        <v>649</v>
-      </c>
-      <c r="C179" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>378</v>
-      </c>
-      <c r="B180" t="s">
-        <v>650</v>
-      </c>
-      <c r="C180" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>379</v>
-      </c>
-      <c r="B181" t="s">
-        <v>651</v>
-      </c>
-      <c r="C181" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>380</v>
-      </c>
-      <c r="B182" t="s">
-        <v>652</v>
-      </c>
-      <c r="C182" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>731</v>
-      </c>
-      <c r="B183" t="s">
-        <v>653</v>
-      </c>
-      <c r="C183" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>381</v>
-      </c>
-      <c r="B184" t="s">
-        <v>654</v>
-      </c>
-      <c r="C184" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>383</v>
-      </c>
-      <c r="B185" t="s">
-        <v>655</v>
-      </c>
-      <c r="C185" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>384</v>
-      </c>
-      <c r="B186" t="s">
-        <v>656</v>
-      </c>
-      <c r="C186" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>732</v>
-      </c>
-      <c r="B187" t="s">
-        <v>657</v>
-      </c>
-      <c r="C187" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>386</v>
-      </c>
-      <c r="B188" t="s">
-        <v>658</v>
-      </c>
-      <c r="C188" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>387</v>
-      </c>
-      <c r="B189" t="s">
-        <v>659</v>
-      </c>
-      <c r="C189" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>388</v>
-      </c>
-      <c r="B190" t="s">
-        <v>660</v>
-      </c>
-      <c r="C190" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>389</v>
-      </c>
-      <c r="B191" t="s">
-        <v>661</v>
-      </c>
-      <c r="C191" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>390</v>
-      </c>
-      <c r="B192" t="s">
-        <v>662</v>
-      </c>
-      <c r="C192" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>391</v>
-      </c>
-      <c r="B193" t="s">
-        <v>663</v>
-      </c>
-      <c r="C193" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>392</v>
-      </c>
-      <c r="B194" t="s">
-        <v>664</v>
-      </c>
-      <c r="C194" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>393</v>
-      </c>
-      <c r="B195" t="s">
-        <v>665</v>
-      </c>
-      <c r="C195" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>394</v>
-      </c>
-      <c r="B196" t="s">
-        <v>666</v>
-      </c>
-      <c r="C196" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>395</v>
-      </c>
-      <c r="B197" t="s">
-        <v>667</v>
-      </c>
-      <c r="C197" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>396</v>
-      </c>
-      <c r="B198" t="s">
-        <v>668</v>
-      </c>
-      <c r="C198" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>398</v>
-      </c>
-      <c r="B199" t="s">
-        <v>669</v>
-      </c>
-      <c r="C199" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>399</v>
-      </c>
-      <c r="B200" t="s">
-        <v>670</v>
-      </c>
-      <c r="C200" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>400</v>
-      </c>
-      <c r="B201" t="s">
-        <v>671</v>
-      </c>
-      <c r="C201" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>402</v>
-      </c>
-      <c r="B202" t="s">
-        <v>672</v>
-      </c>
-      <c r="C202" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>403</v>
-      </c>
-      <c r="B203" t="s">
-        <v>673</v>
-      </c>
-      <c r="C203" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>404</v>
-      </c>
-      <c r="B204" t="s">
-        <v>674</v>
-      </c>
-      <c r="C204" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>405</v>
-      </c>
-      <c r="B205" t="s">
-        <v>675</v>
-      </c>
-      <c r="C205" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>406</v>
-      </c>
-      <c r="B206" t="s">
-        <v>676</v>
-      </c>
-      <c r="C206" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>407</v>
-      </c>
-      <c r="B207" t="s">
-        <v>677</v>
-      </c>
-      <c r="C207" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>408</v>
-      </c>
-      <c r="B208" t="s">
-        <v>678</v>
-      </c>
-      <c r="C208" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>409</v>
-      </c>
-      <c r="B209" t="s">
-        <v>679</v>
-      </c>
-      <c r="C209" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>410</v>
-      </c>
-      <c r="B210" t="s">
-        <v>680</v>
-      </c>
-      <c r="C210" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>411</v>
-      </c>
-      <c r="B211" t="s">
-        <v>681</v>
-      </c>
-      <c r="C211" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>412</v>
-      </c>
-      <c r="B212" t="s">
-        <v>682</v>
-      </c>
-      <c r="C212" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>413</v>
-      </c>
-      <c r="B213" t="s">
-        <v>683</v>
-      </c>
-      <c r="C213" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>414</v>
-      </c>
-      <c r="B214" t="s">
-        <v>684</v>
-      </c>
-      <c r="C214" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>415</v>
-      </c>
-      <c r="B215" t="s">
-        <v>685</v>
-      </c>
-      <c r="C215" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>416</v>
-      </c>
-      <c r="B216" t="s">
-        <v>686</v>
-      </c>
-      <c r="C216" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>417</v>
-      </c>
-      <c r="B217" t="s">
-        <v>687</v>
-      </c>
-      <c r="C217" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>418</v>
-      </c>
-      <c r="B218" t="s">
-        <v>687</v>
-      </c>
-      <c r="C218" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>419</v>
-      </c>
-      <c r="B219" t="s">
-        <v>688</v>
-      </c>
-      <c r="C219" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>420</v>
-      </c>
-      <c r="B220" t="s">
-        <v>689</v>
-      </c>
-      <c r="C220" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>421</v>
-      </c>
-      <c r="B221" t="s">
-        <v>690</v>
-      </c>
-      <c r="C221" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>422</v>
-      </c>
-      <c r="B222" t="s">
-        <v>691</v>
-      </c>
-      <c r="C222" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>423</v>
-      </c>
-      <c r="B223" t="s">
-        <v>692</v>
-      </c>
-      <c r="C223" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>424</v>
-      </c>
-      <c r="B224" t="s">
-        <v>693</v>
-      </c>
-      <c r="C224" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>425</v>
-      </c>
-      <c r="B225" t="s">
-        <v>694</v>
-      </c>
-      <c r="C225" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>426</v>
-      </c>
-      <c r="B226" t="s">
-        <v>695</v>
-      </c>
-      <c r="C226" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>427</v>
-      </c>
-      <c r="B227" t="s">
-        <v>696</v>
-      </c>
-      <c r="C227" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>428</v>
-      </c>
-      <c r="B228" t="s">
-        <v>697</v>
-      </c>
-      <c r="C228" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>429</v>
-      </c>
-      <c r="B229" t="s">
-        <v>698</v>
-      </c>
-      <c r="C229" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>430</v>
-      </c>
-      <c r="B230" t="s">
-        <v>699</v>
-      </c>
-      <c r="C230" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>431</v>
-      </c>
-      <c r="B231" t="s">
-        <v>700</v>
-      </c>
-      <c r="C231" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>432</v>
-      </c>
-      <c r="B232" t="s">
-        <v>701</v>
-      </c>
-      <c r="C232" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>434</v>
-      </c>
-      <c r="B233" t="s">
-        <v>702</v>
-      </c>
-      <c r="C233" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>435</v>
-      </c>
-      <c r="B234" t="s">
-        <v>703</v>
-      </c>
-      <c r="C234" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>436</v>
-      </c>
-      <c r="B235" t="s">
-        <v>704</v>
-      </c>
-      <c r="C235" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>437</v>
-      </c>
-      <c r="B236" t="s">
-        <v>705</v>
-      </c>
-      <c r="C236" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>438</v>
-      </c>
-      <c r="B237" t="s">
-        <v>706</v>
-      </c>
-      <c r="C237" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>439</v>
-      </c>
-      <c r="B238" t="s">
-        <v>707</v>
-      </c>
-      <c r="C238" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>440</v>
-      </c>
-      <c r="B239" t="s">
-        <v>708</v>
-      </c>
-      <c r="C239" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>442</v>
-      </c>
-      <c r="B240" t="s">
-        <v>709</v>
-      </c>
-      <c r="C240" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>443</v>
-      </c>
-      <c r="B241" t="s">
-        <v>710</v>
-      </c>
-      <c r="C241" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>444</v>
-      </c>
-      <c r="B242" t="s">
-        <v>711</v>
-      </c>
-      <c r="C242" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>445</v>
-      </c>
-      <c r="B243" t="s">
-        <v>712</v>
-      </c>
-      <c r="C243" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>446</v>
-      </c>
-      <c r="B244" t="s">
-        <v>713</v>
-      </c>
-      <c r="C244" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
-        <v>447</v>
-      </c>
-      <c r="B245" t="s">
-        <v>714</v>
-      </c>
-      <c r="C245" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
-        <v>448</v>
-      </c>
-      <c r="B246" t="s">
-        <v>715</v>
-      </c>
-      <c r="C246" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>449</v>
-      </c>
-      <c r="B247" t="s">
-        <v>716</v>
-      </c>
-      <c r="C247" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>450</v>
-      </c>
-      <c r="B248" t="s">
-        <v>717</v>
-      </c>
-      <c r="C248" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>733</v>
-      </c>
-      <c r="B249" t="s">
-        <v>718</v>
-      </c>
-      <c r="C249" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
-        <v>452</v>
-      </c>
-      <c r="B250" t="s">
-        <v>719</v>
-      </c>
-      <c r="C250" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>453</v>
-      </c>
-      <c r="B251" t="s">
-        <v>720</v>
-      </c>
-      <c r="C251" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>454</v>
-      </c>
-      <c r="B252" t="s">
-        <v>721</v>
-      </c>
-      <c r="C252" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>455</v>
-      </c>
-      <c r="B253" t="s">
-        <v>722</v>
-      </c>
-      <c r="C253" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>456</v>
-      </c>
-      <c r="B254" t="s">
-        <v>723</v>
-      </c>
-      <c r="C254" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>457</v>
-      </c>
-      <c r="B255" t="s">
-        <v>724</v>
-      </c>
-      <c r="C255" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>458</v>
-      </c>
-      <c r="B256" t="s">
-        <v>725</v>
-      </c>
-      <c r="C256" t="s">
-        <v>80</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/spreadsheet.xlsx
+++ b/spreadsheet.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loren\Desktop\MK1212-website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BD67BC-FD56-485A-9D97-5F48D3A42BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C22842-C87A-4F37-9C87-C514B1AA7BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2003C0B9-FD41-4D78-AC63-D37F7559A3C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
-    <sheet name="Foglio3" sheetId="3" r:id="rId3"/>
+    <sheet name="Foglio4" sheetId="4" r:id="rId2"/>
+    <sheet name="Foglio2" sheetId="2" r:id="rId3"/>
+    <sheet name="Foglio3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$D$552</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Foglio4!$C$1:$C$1000</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2809" uniqueCount="1500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3519" uniqueCount="1517">
   <si>
     <t>false</t>
   </si>
@@ -4541,6 +4543,57 @@
   </si>
   <si>
     <t>Faction Colour</t>
+  </si>
+  <si>
+    <t>Region_key</t>
+  </si>
+  <si>
+    <t>Projected owner (map)</t>
+  </si>
+  <si>
+    <t>mk_fact_yemen</t>
+  </si>
+  <si>
+    <t>mk_fact_staufer</t>
+  </si>
+  <si>
+    <t>mk_fact_rhine</t>
+  </si>
+  <si>
+    <t>mk_fact_prussia</t>
+  </si>
+  <si>
+    <t>mk_fact_hanse</t>
+  </si>
+  <si>
+    <t>mk_fact_masovia</t>
+  </si>
+  <si>
+    <t>mk_fact_tripoli</t>
+  </si>
+  <si>
+    <t>Yemen</t>
+  </si>
+  <si>
+    <t>Staufer</t>
+  </si>
+  <si>
+    <t>Rhine</t>
+  </si>
+  <si>
+    <t>Prussia</t>
+  </si>
+  <si>
+    <t>Hanse</t>
+  </si>
+  <si>
+    <t>mk_fact_desolate</t>
+  </si>
+  <si>
+    <t>Desolate</t>
+  </si>
+  <si>
+    <t>Masovia</t>
   </si>
 </sst>
 </file>
@@ -4556,12 +4609,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -4576,10 +4635,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -4922,6 +4982,7 @@
     <col min="1" max="1" width="43.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4998,7 +5059,7 @@
         <v>471</v>
       </c>
       <c r="E4" t="s">
-        <v>874</v>
+        <v>1509</v>
       </c>
       <c r="F4" t="s">
         <v>1365</v>
@@ -5098,7 +5159,7 @@
         <v>476</v>
       </c>
       <c r="E9" t="s">
-        <v>874</v>
+        <v>913</v>
       </c>
       <c r="F9" t="s">
         <v>1365</v>
@@ -5118,7 +5179,7 @@
         <v>477</v>
       </c>
       <c r="E10" t="s">
-        <v>874</v>
+        <v>863</v>
       </c>
       <c r="F10" t="s">
         <v>1365</v>
@@ -5138,7 +5199,7 @@
         <v>478</v>
       </c>
       <c r="E11" t="s">
-        <v>874</v>
+        <v>863</v>
       </c>
       <c r="F11" t="s">
         <v>1365</v>
@@ -5198,7 +5259,7 @@
         <v>481</v>
       </c>
       <c r="E14" t="s">
-        <v>926</v>
+        <v>875</v>
       </c>
       <c r="F14" t="s">
         <v>1391</v>
@@ -5598,7 +5659,7 @@
         <v>501</v>
       </c>
       <c r="E34" t="s">
-        <v>1116</v>
+        <v>952</v>
       </c>
       <c r="F34" t="s">
         <v>1456</v>
@@ -6158,7 +6219,7 @@
         <v>529</v>
       </c>
       <c r="E62" t="s">
-        <v>891</v>
+        <v>928</v>
       </c>
       <c r="F62" t="s">
         <v>1373</v>
@@ -6198,7 +6259,7 @@
         <v>531</v>
       </c>
       <c r="E64" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="F64" t="s">
         <v>1365</v>
@@ -6258,7 +6319,7 @@
         <v>534</v>
       </c>
       <c r="E67" t="s">
-        <v>921</v>
+        <v>895</v>
       </c>
       <c r="F67" t="s">
         <v>1386</v>
@@ -6358,7 +6419,7 @@
         <v>539</v>
       </c>
       <c r="E72" t="s">
-        <v>915</v>
+        <v>936</v>
       </c>
       <c r="F72" t="s">
         <v>1469</v>
@@ -6458,7 +6519,7 @@
         <v>544</v>
       </c>
       <c r="E77" t="s">
-        <v>896</v>
+        <v>864</v>
       </c>
       <c r="F77" t="s">
         <v>1349</v>
@@ -6558,7 +6619,7 @@
         <v>549</v>
       </c>
       <c r="E82" t="s">
-        <v>926</v>
+        <v>904</v>
       </c>
       <c r="F82" t="s">
         <v>1391</v>
@@ -6718,7 +6779,7 @@
         <v>557</v>
       </c>
       <c r="E90" t="s">
-        <v>893</v>
+        <v>915</v>
       </c>
       <c r="F90" t="s">
         <v>1375</v>
@@ -6738,7 +6799,7 @@
         <v>558</v>
       </c>
       <c r="E91" t="s">
-        <v>915</v>
+        <v>1511</v>
       </c>
       <c r="F91" t="s">
         <v>1469</v>
@@ -6778,7 +6839,7 @@
         <v>560</v>
       </c>
       <c r="E93" t="s">
-        <v>874</v>
+        <v>913</v>
       </c>
       <c r="F93" t="s">
         <v>1365</v>
@@ -7038,7 +7099,7 @@
         <v>573</v>
       </c>
       <c r="E106" t="s">
-        <v>1123</v>
+        <v>929</v>
       </c>
       <c r="F106" t="s">
         <v>1458</v>
@@ -7058,7 +7119,7 @@
         <v>574</v>
       </c>
       <c r="E107" t="s">
-        <v>1117</v>
+        <v>1512</v>
       </c>
       <c r="F107" t="s">
         <v>1339</v>
@@ -7078,7 +7139,7 @@
         <v>575</v>
       </c>
       <c r="E108" t="s">
-        <v>876</v>
+        <v>1510</v>
       </c>
       <c r="F108" t="s">
         <v>1349</v>
@@ -7138,7 +7199,7 @@
         <v>578</v>
       </c>
       <c r="E111" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="F111" t="s">
         <v>1373</v>
@@ -7198,7 +7259,7 @@
         <v>581</v>
       </c>
       <c r="E114" t="s">
-        <v>886</v>
+        <v>932</v>
       </c>
       <c r="F114" t="s">
         <v>1371</v>
@@ -7278,7 +7339,7 @@
         <v>585</v>
       </c>
       <c r="E118" t="s">
-        <v>915</v>
+        <v>1513</v>
       </c>
       <c r="F118" t="s">
         <v>1469</v>
@@ -7378,7 +7439,7 @@
         <v>590</v>
       </c>
       <c r="E123" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="F123" t="s">
         <v>1343</v>
@@ -7398,7 +7459,7 @@
         <v>591</v>
       </c>
       <c r="E124" t="s">
-        <v>896</v>
+        <v>1509</v>
       </c>
       <c r="F124" t="s">
         <v>1349</v>
@@ -7438,7 +7499,7 @@
         <v>593</v>
       </c>
       <c r="E126" t="s">
-        <v>937</v>
+        <v>1515</v>
       </c>
       <c r="F126" t="s">
         <v>1394</v>
@@ -7518,7 +7579,7 @@
         <v>597</v>
       </c>
       <c r="E130" t="s">
-        <v>934</v>
+        <v>960</v>
       </c>
       <c r="F130" t="s">
         <v>1393</v>
@@ -7658,7 +7719,7 @@
         <v>604</v>
       </c>
       <c r="E137" t="s">
-        <v>927</v>
+        <v>1129</v>
       </c>
       <c r="F137" t="s">
         <v>1392</v>
@@ -7718,7 +7779,7 @@
         <v>607</v>
       </c>
       <c r="E140" t="s">
-        <v>899</v>
+        <v>882</v>
       </c>
       <c r="F140" t="s">
         <v>1378</v>
@@ -7738,7 +7799,7 @@
         <v>608</v>
       </c>
       <c r="E141" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="F141" t="s">
         <v>1339</v>
@@ -7838,7 +7899,7 @@
         <v>613</v>
       </c>
       <c r="E146" t="s">
-        <v>927</v>
+        <v>953</v>
       </c>
       <c r="F146" t="s">
         <v>1392</v>
@@ -7918,7 +7979,7 @@
         <v>617</v>
       </c>
       <c r="E150" t="s">
-        <v>1116</v>
+        <v>952</v>
       </c>
       <c r="F150" t="s">
         <v>1456</v>
@@ -7938,7 +7999,7 @@
         <v>618</v>
       </c>
       <c r="E151" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="F151" t="s">
         <v>1339</v>
@@ -8038,7 +8099,7 @@
         <v>623</v>
       </c>
       <c r="E156" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
       <c r="F156" t="s">
         <v>1392</v>
@@ -8098,7 +8159,7 @@
         <v>626</v>
       </c>
       <c r="E159" t="s">
-        <v>933</v>
+        <v>1516</v>
       </c>
       <c r="F159" t="s">
         <v>1339</v>
@@ -8138,7 +8199,7 @@
         <v>628</v>
       </c>
       <c r="E161" t="s">
-        <v>927</v>
+        <v>960</v>
       </c>
       <c r="F161" t="s">
         <v>1392</v>
@@ -8198,7 +8259,7 @@
         <v>631</v>
       </c>
       <c r="E164" t="s">
-        <v>927</v>
+        <v>953</v>
       </c>
       <c r="F164" t="s">
         <v>1392</v>
@@ -8218,7 +8279,7 @@
         <v>632</v>
       </c>
       <c r="E165" t="s">
-        <v>858</v>
+        <v>1126</v>
       </c>
       <c r="F165" t="s">
         <v>1472</v>
@@ -8238,7 +8299,7 @@
         <v>633</v>
       </c>
       <c r="E166" t="s">
-        <v>909</v>
+        <v>874</v>
       </c>
       <c r="F166" t="s">
         <v>1381</v>
@@ -8258,7 +8319,7 @@
         <v>634</v>
       </c>
       <c r="E167" t="s">
-        <v>874</v>
+        <v>909</v>
       </c>
       <c r="F167" t="s">
         <v>1365</v>
@@ -8318,7 +8379,7 @@
         <v>637</v>
       </c>
       <c r="E170" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="F170" t="s">
         <v>1339</v>
@@ -8458,7 +8519,7 @@
         <v>644</v>
       </c>
       <c r="E177" t="s">
-        <v>1129</v>
+        <v>995</v>
       </c>
       <c r="F177" t="s">
         <v>1496</v>
@@ -8518,7 +8579,7 @@
         <v>647</v>
       </c>
       <c r="E180" t="s">
-        <v>886</v>
+        <v>932</v>
       </c>
       <c r="F180" t="s">
         <v>1371</v>
@@ -8538,7 +8599,7 @@
         <v>648</v>
       </c>
       <c r="E181" t="s">
-        <v>891</v>
+        <v>928</v>
       </c>
       <c r="F181" t="s">
         <v>1373</v>
@@ -8678,7 +8739,7 @@
         <v>655</v>
       </c>
       <c r="E188" t="s">
-        <v>927</v>
+        <v>1113</v>
       </c>
       <c r="F188" t="s">
         <v>1392</v>
@@ -8818,7 +8879,7 @@
         <v>662</v>
       </c>
       <c r="E195" t="s">
-        <v>891</v>
+        <v>928</v>
       </c>
       <c r="F195" t="s">
         <v>1373</v>
@@ -8838,7 +8899,7 @@
         <v>663</v>
       </c>
       <c r="E196" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="F196" t="s">
         <v>1339</v>
@@ -8918,7 +8979,7 @@
         <v>667</v>
       </c>
       <c r="E200" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="F200" t="s">
         <v>1339</v>
@@ -9038,7 +9099,7 @@
         <v>673</v>
       </c>
       <c r="E206" t="s">
-        <v>864</v>
+        <v>1120</v>
       </c>
       <c r="F206" t="s">
         <v>1343</v>
@@ -9138,7 +9199,7 @@
         <v>678</v>
       </c>
       <c r="E211" t="s">
-        <v>922</v>
+        <v>678</v>
       </c>
       <c r="F211" t="s">
         <v>1387</v>
@@ -9218,7 +9279,7 @@
         <v>681</v>
       </c>
       <c r="E215" t="s">
-        <v>927</v>
+        <v>1129</v>
       </c>
       <c r="F215" t="s">
         <v>1392</v>
@@ -9458,7 +9519,7 @@
         <v>693</v>
       </c>
       <c r="E227" t="s">
-        <v>1109</v>
+        <v>879</v>
       </c>
       <c r="F227" t="s">
         <v>1454</v>
@@ -9478,7 +9539,7 @@
         <v>694</v>
       </c>
       <c r="E228" t="s">
-        <v>927</v>
+        <v>1129</v>
       </c>
       <c r="F228" t="s">
         <v>1392</v>
@@ -9558,7 +9619,7 @@
         <v>698</v>
       </c>
       <c r="E232" t="s">
-        <v>927</v>
+        <v>1133</v>
       </c>
       <c r="F232" t="s">
         <v>1392</v>
@@ -9678,7 +9739,7 @@
         <v>704</v>
       </c>
       <c r="E238" t="s">
-        <v>1135</v>
+        <v>917</v>
       </c>
       <c r="F238" t="s">
         <v>1498</v>
@@ -10071,6 +10132,2625 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20F1F7E7-608A-4374-928A-8F3661ADB9B1}">
+  <dimension ref="A1:C237"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" t="s">
+        <v>774</v>
+      </c>
+      <c r="C2" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s">
+        <v>854</v>
+      </c>
+      <c r="C3" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" t="s">
+        <v>844</v>
+      </c>
+      <c r="C5" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" t="s">
+        <v>775</v>
+      </c>
+      <c r="C6" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" t="s">
+        <v>776</v>
+      </c>
+      <c r="C7" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" t="s">
+        <v>777</v>
+      </c>
+      <c r="C8" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C9" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C10" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C11" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" t="s">
+        <v>771</v>
+      </c>
+      <c r="C12" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B13" t="s">
+        <v>778</v>
+      </c>
+      <c r="C13" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C14" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" t="s">
+        <v>780</v>
+      </c>
+      <c r="C15" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B16" t="s">
+        <v>806</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" t="s">
+        <v>853</v>
+      </c>
+      <c r="C17" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B18" t="s">
+        <v>781</v>
+      </c>
+      <c r="C18" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" t="s">
+        <v>771</v>
+      </c>
+      <c r="C19" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>197</v>
+      </c>
+      <c r="B20" t="s">
+        <v>846</v>
+      </c>
+      <c r="C20" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" t="s">
+        <v>839</v>
+      </c>
+      <c r="C21" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" t="s">
+        <v>782</v>
+      </c>
+      <c r="C22" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" t="s">
+        <v>806</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>202</v>
+      </c>
+      <c r="B25" t="s">
+        <v>771</v>
+      </c>
+      <c r="C25" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>203</v>
+      </c>
+      <c r="B26" t="s">
+        <v>778</v>
+      </c>
+      <c r="C26" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>204</v>
+      </c>
+      <c r="B27" t="s">
+        <v>773</v>
+      </c>
+      <c r="C27" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>205</v>
+      </c>
+      <c r="B28" t="s">
+        <v>783</v>
+      </c>
+      <c r="C28" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>206</v>
+      </c>
+      <c r="B29" t="s">
+        <v>784</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" t="s">
+        <v>779</v>
+      </c>
+      <c r="C30" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>208</v>
+      </c>
+      <c r="B31" t="s">
+        <v>771</v>
+      </c>
+      <c r="C31" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>209</v>
+      </c>
+      <c r="B32" t="s">
+        <v>785</v>
+      </c>
+      <c r="C32" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>210</v>
+      </c>
+      <c r="B33" t="s">
+        <v>773</v>
+      </c>
+      <c r="C33" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>300</v>
+      </c>
+      <c r="B34" t="s">
+        <v>804</v>
+      </c>
+      <c r="C34" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>211</v>
+      </c>
+      <c r="B35" t="s">
+        <v>807</v>
+      </c>
+      <c r="C35" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>212</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C36" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>214</v>
+      </c>
+      <c r="B37" t="s">
+        <v>787</v>
+      </c>
+      <c r="C37" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>215</v>
+      </c>
+      <c r="B38" t="s">
+        <v>849</v>
+      </c>
+      <c r="C38" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>216</v>
+      </c>
+      <c r="B39" t="s">
+        <v>848</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>218</v>
+      </c>
+      <c r="B40" t="s">
+        <v>789</v>
+      </c>
+      <c r="C40" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>219</v>
+      </c>
+      <c r="B41" t="s">
+        <v>790</v>
+      </c>
+      <c r="C41" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>220</v>
+      </c>
+      <c r="B42" t="s">
+        <v>791</v>
+      </c>
+      <c r="C42" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>222</v>
+      </c>
+      <c r="B43" t="s">
+        <v>793</v>
+      </c>
+      <c r="C43" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>223</v>
+      </c>
+      <c r="B44" t="s">
+        <v>790</v>
+      </c>
+      <c r="C44" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>224</v>
+      </c>
+      <c r="B45" t="s">
+        <v>794</v>
+      </c>
+      <c r="C45" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>225</v>
+      </c>
+      <c r="B46" t="s">
+        <v>779</v>
+      </c>
+      <c r="C46" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>226</v>
+      </c>
+      <c r="B47" t="s">
+        <v>830</v>
+      </c>
+      <c r="C47" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>227</v>
+      </c>
+      <c r="B48" t="s">
+        <v>845</v>
+      </c>
+      <c r="C48" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>228</v>
+      </c>
+      <c r="B49" t="s">
+        <v>795</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>229</v>
+      </c>
+      <c r="B50" t="s">
+        <v>831</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>230</v>
+      </c>
+      <c r="B51" t="s">
+        <v>796</v>
+      </c>
+      <c r="C51" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>231</v>
+      </c>
+      <c r="B52" t="s">
+        <v>771</v>
+      </c>
+      <c r="C52" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>232</v>
+      </c>
+      <c r="B53" t="s">
+        <v>797</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>233</v>
+      </c>
+      <c r="B54" t="s">
+        <v>798</v>
+      </c>
+      <c r="C54" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>234</v>
+      </c>
+      <c r="B55" t="s">
+        <v>790</v>
+      </c>
+      <c r="C55" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>235</v>
+      </c>
+      <c r="B56" t="s">
+        <v>842</v>
+      </c>
+      <c r="C56" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>236</v>
+      </c>
+      <c r="B57" t="s">
+        <v>778</v>
+      </c>
+      <c r="C57" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>237</v>
+      </c>
+      <c r="B58" t="s">
+        <v>803</v>
+      </c>
+      <c r="C58" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>238</v>
+      </c>
+      <c r="B59" t="s">
+        <v>842</v>
+      </c>
+      <c r="C59" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>239</v>
+      </c>
+      <c r="B60" t="s">
+        <v>771</v>
+      </c>
+      <c r="C60" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>240</v>
+      </c>
+      <c r="B61" t="s">
+        <v>771</v>
+      </c>
+      <c r="C61" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>241</v>
+      </c>
+      <c r="B62" t="s">
+        <v>843</v>
+      </c>
+      <c r="C62" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>242</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C63" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>243</v>
+      </c>
+      <c r="B64" t="s">
+        <v>800</v>
+      </c>
+      <c r="C64" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>244</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C65" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>246</v>
+      </c>
+      <c r="B66" t="s">
+        <v>801</v>
+      </c>
+      <c r="C66" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>247</v>
+      </c>
+      <c r="B67" t="s">
+        <v>799</v>
+      </c>
+      <c r="C67" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>248</v>
+      </c>
+      <c r="B68" t="s">
+        <v>790</v>
+      </c>
+      <c r="C68" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>249</v>
+      </c>
+      <c r="B69" t="s">
+        <v>804</v>
+      </c>
+      <c r="C69" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>250</v>
+      </c>
+      <c r="B70" t="s">
+        <v>839</v>
+      </c>
+      <c r="C70" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>251</v>
+      </c>
+      <c r="B71" t="s">
+        <v>805</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>252</v>
+      </c>
+      <c r="B72" t="s">
+        <v>772</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>253</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C73" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>255</v>
+      </c>
+      <c r="B74" t="s">
+        <v>806</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>256</v>
+      </c>
+      <c r="B75" t="s">
+        <v>807</v>
+      </c>
+      <c r="C75" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>257</v>
+      </c>
+      <c r="B76" t="s">
+        <v>778</v>
+      </c>
+      <c r="C76" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>258</v>
+      </c>
+      <c r="B77" t="s">
+        <v>854</v>
+      </c>
+      <c r="C77" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>259</v>
+      </c>
+      <c r="B78" t="s">
+        <v>778</v>
+      </c>
+      <c r="C78" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>260</v>
+      </c>
+      <c r="B79" t="s">
+        <v>793</v>
+      </c>
+      <c r="C79" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>261</v>
+      </c>
+      <c r="B80" t="s">
+        <v>808</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>262</v>
+      </c>
+      <c r="B81" t="s">
+        <v>850</v>
+      </c>
+      <c r="C81" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>263</v>
+      </c>
+      <c r="B82" t="s">
+        <v>776</v>
+      </c>
+      <c r="C82" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>264</v>
+      </c>
+      <c r="B83" t="s">
+        <v>843</v>
+      </c>
+      <c r="C83" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>265</v>
+      </c>
+      <c r="B84" t="s">
+        <v>779</v>
+      </c>
+      <c r="C84" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>266</v>
+      </c>
+      <c r="B85" t="s">
+        <v>778</v>
+      </c>
+      <c r="C85" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>268</v>
+      </c>
+      <c r="B86" t="s">
+        <v>809</v>
+      </c>
+      <c r="C86" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>269</v>
+      </c>
+      <c r="B87" t="s">
+        <v>810</v>
+      </c>
+      <c r="C87" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>270</v>
+      </c>
+      <c r="B88" t="s">
+        <v>807</v>
+      </c>
+      <c r="C88" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>271</v>
+      </c>
+      <c r="B89" t="s">
+        <v>811</v>
+      </c>
+      <c r="C89" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>272</v>
+      </c>
+      <c r="B90" t="s">
+        <v>779</v>
+      </c>
+      <c r="C90" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>273</v>
+      </c>
+      <c r="B91" t="s">
+        <v>793</v>
+      </c>
+      <c r="C91" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>274</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>275</v>
+      </c>
+      <c r="B93" t="s">
+        <v>779</v>
+      </c>
+      <c r="C93" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>276</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C94" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>278</v>
+      </c>
+      <c r="B95" t="s">
+        <v>845</v>
+      </c>
+      <c r="C95" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>279</v>
+      </c>
+      <c r="B96" t="s">
+        <v>806</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>280</v>
+      </c>
+      <c r="B97" t="s">
+        <v>805</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>281</v>
+      </c>
+      <c r="B98" t="s">
+        <v>779</v>
+      </c>
+      <c r="C98" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>283</v>
+      </c>
+      <c r="B99" t="s">
+        <v>771</v>
+      </c>
+      <c r="C99" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>284</v>
+      </c>
+      <c r="B100" t="s">
+        <v>815</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>285</v>
+      </c>
+      <c r="B101" t="s">
+        <v>779</v>
+      </c>
+      <c r="C101" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>287</v>
+      </c>
+      <c r="B102" t="s">
+        <v>807</v>
+      </c>
+      <c r="C102" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>289</v>
+      </c>
+      <c r="B103" t="s">
+        <v>806</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>290</v>
+      </c>
+      <c r="B104" t="s">
+        <v>771</v>
+      </c>
+      <c r="C104" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>291</v>
+      </c>
+      <c r="B105" t="s">
+        <v>779</v>
+      </c>
+      <c r="C105" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>292</v>
+      </c>
+      <c r="B106" t="s">
+        <v>788</v>
+      </c>
+      <c r="C106" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>293</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C107" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>294</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>297</v>
+      </c>
+      <c r="B109" t="s">
+        <v>813</v>
+      </c>
+      <c r="C109" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>298</v>
+      </c>
+      <c r="B110" t="s">
+        <v>773</v>
+      </c>
+      <c r="C110" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>299</v>
+      </c>
+      <c r="B111" t="s">
+        <v>798</v>
+      </c>
+      <c r="C111" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>301</v>
+      </c>
+      <c r="B112" t="s">
+        <v>814</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>302</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C113" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>303</v>
+      </c>
+      <c r="B114" t="s">
+        <v>791</v>
+      </c>
+      <c r="C114" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>304</v>
+      </c>
+      <c r="B115" t="s">
+        <v>815</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>306</v>
+      </c>
+      <c r="B116" t="s">
+        <v>790</v>
+      </c>
+      <c r="C116" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>307</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>309</v>
+      </c>
+      <c r="B118" t="s">
+        <v>816</v>
+      </c>
+      <c r="C118" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>221</v>
+      </c>
+      <c r="B119" t="s">
+        <v>792</v>
+      </c>
+      <c r="C119" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>310</v>
+      </c>
+      <c r="B120" t="s">
+        <v>817</v>
+      </c>
+      <c r="C120" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>311</v>
+      </c>
+      <c r="B121" t="s">
+        <v>778</v>
+      </c>
+      <c r="C121" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>312</v>
+      </c>
+      <c r="B122" t="s">
+        <v>806</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>313</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C123" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>314</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>315</v>
+      </c>
+      <c r="B125" t="s">
+        <v>778</v>
+      </c>
+      <c r="C125" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>316</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>317</v>
+      </c>
+      <c r="B127" t="s">
+        <v>818</v>
+      </c>
+      <c r="C127" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>318</v>
+      </c>
+      <c r="B128" t="s">
+        <v>779</v>
+      </c>
+      <c r="C128" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>319</v>
+      </c>
+      <c r="B129" t="s">
+        <v>819</v>
+      </c>
+      <c r="C129" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>320</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C130" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>322</v>
+      </c>
+      <c r="B131" t="s">
+        <v>771</v>
+      </c>
+      <c r="C131" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>323</v>
+      </c>
+      <c r="B132" t="s">
+        <v>777</v>
+      </c>
+      <c r="C132" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>324</v>
+      </c>
+      <c r="B133" t="s">
+        <v>820</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>325</v>
+      </c>
+      <c r="B134" t="s">
+        <v>772</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>327</v>
+      </c>
+      <c r="B135" t="s">
+        <v>778</v>
+      </c>
+      <c r="C135" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>328</v>
+      </c>
+      <c r="B136" t="s">
+        <v>847</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>330</v>
+      </c>
+      <c r="B137" t="s">
+        <v>840</v>
+      </c>
+      <c r="C137" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>331</v>
+      </c>
+      <c r="B138" t="s">
+        <v>821</v>
+      </c>
+      <c r="C138" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>332</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C139" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>334</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>335</v>
+      </c>
+      <c r="B141" t="s">
+        <v>799</v>
+      </c>
+      <c r="C141" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>336</v>
+      </c>
+      <c r="B142" t="s">
+        <v>786</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>337</v>
+      </c>
+      <c r="B143" t="s">
+        <v>779</v>
+      </c>
+      <c r="C143" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>338</v>
+      </c>
+      <c r="B144" t="s">
+        <v>790</v>
+      </c>
+      <c r="C144" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>339</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C145" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>341</v>
+      </c>
+      <c r="B146" t="s">
+        <v>793</v>
+      </c>
+      <c r="C146" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>343</v>
+      </c>
+      <c r="B147" t="s">
+        <v>824</v>
+      </c>
+      <c r="C147" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>344</v>
+      </c>
+      <c r="B148" t="s">
+        <v>816</v>
+      </c>
+      <c r="C148" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>345</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C149" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>347</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>348</v>
+      </c>
+      <c r="B151" t="s">
+        <v>778</v>
+      </c>
+      <c r="C151" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>349</v>
+      </c>
+      <c r="B152" t="s">
+        <v>822</v>
+      </c>
+      <c r="C152" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>350</v>
+      </c>
+      <c r="B153" t="s">
+        <v>816</v>
+      </c>
+      <c r="C153" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>351</v>
+      </c>
+      <c r="B154" t="s">
+        <v>807</v>
+      </c>
+      <c r="C154" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>352</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C155" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>354</v>
+      </c>
+      <c r="B156" t="s">
+        <v>842</v>
+      </c>
+      <c r="C156" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>355</v>
+      </c>
+      <c r="B157" t="s">
+        <v>796</v>
+      </c>
+      <c r="C157" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>356</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>358</v>
+      </c>
+      <c r="B159" t="s">
+        <v>816</v>
+      </c>
+      <c r="C159" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>359</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C160" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>361</v>
+      </c>
+      <c r="B161" t="s">
+        <v>823</v>
+      </c>
+      <c r="C161" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>362</v>
+      </c>
+      <c r="B162" t="s">
+        <v>824</v>
+      </c>
+      <c r="C162" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>363</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C163" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>364</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>365</v>
+      </c>
+      <c r="B165" t="s">
+        <v>771</v>
+      </c>
+      <c r="C165" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>366</v>
+      </c>
+      <c r="B166" t="s">
+        <v>777</v>
+      </c>
+      <c r="C166" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>367</v>
+      </c>
+      <c r="B167" t="s">
+        <v>786</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>368</v>
+      </c>
+      <c r="B168" t="s">
+        <v>779</v>
+      </c>
+      <c r="C168" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>326</v>
+      </c>
+      <c r="B169" t="s">
+        <v>812</v>
+      </c>
+      <c r="C169" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>369</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C170" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>370</v>
+      </c>
+      <c r="B171" t="s">
+        <v>816</v>
+      </c>
+      <c r="C171" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>371</v>
+      </c>
+      <c r="B172" t="s">
+        <v>799</v>
+      </c>
+      <c r="C172" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>372</v>
+      </c>
+      <c r="B173" t="s">
+        <v>851</v>
+      </c>
+      <c r="C173" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>373</v>
+      </c>
+      <c r="B174" t="s">
+        <v>825</v>
+      </c>
+      <c r="C174" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>374</v>
+      </c>
+      <c r="B175" t="s">
+        <v>774</v>
+      </c>
+      <c r="C175" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>376</v>
+      </c>
+      <c r="B176" t="s">
+        <v>816</v>
+      </c>
+      <c r="C176" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>377</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C177" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>378</v>
+      </c>
+      <c r="B178" t="s">
+        <v>778</v>
+      </c>
+      <c r="C178" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>379</v>
+      </c>
+      <c r="B179" t="s">
+        <v>779</v>
+      </c>
+      <c r="C179" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>381</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C180" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>382</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C181" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>398</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C182" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>384</v>
+      </c>
+      <c r="B183" t="s">
+        <v>826</v>
+      </c>
+      <c r="C183" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>385</v>
+      </c>
+      <c r="B184" t="s">
+        <v>778</v>
+      </c>
+      <c r="C184" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>386</v>
+      </c>
+      <c r="B185" t="s">
+        <v>849</v>
+      </c>
+      <c r="C185" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>387</v>
+      </c>
+      <c r="B186" t="s">
+        <v>845</v>
+      </c>
+      <c r="C186" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>388</v>
+      </c>
+      <c r="B187" t="s">
+        <v>831</v>
+      </c>
+      <c r="C187" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>389</v>
+      </c>
+      <c r="B188" t="s">
+        <v>852</v>
+      </c>
+      <c r="C188" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>390</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C189" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>391</v>
+      </c>
+      <c r="B190" t="s">
+        <v>799</v>
+      </c>
+      <c r="C190" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>392</v>
+      </c>
+      <c r="B191" t="s">
+        <v>827</v>
+      </c>
+      <c r="C191" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>393</v>
+      </c>
+      <c r="B192" t="s">
+        <v>826</v>
+      </c>
+      <c r="C192" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>394</v>
+      </c>
+      <c r="B193" t="s">
+        <v>815</v>
+      </c>
+      <c r="C193" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>396</v>
+      </c>
+      <c r="B194" t="s">
+        <v>774</v>
+      </c>
+      <c r="C194" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>397</v>
+      </c>
+      <c r="B195" t="s">
+        <v>849</v>
+      </c>
+      <c r="C195" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>400</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>401</v>
+      </c>
+      <c r="B197" t="s">
+        <v>846</v>
+      </c>
+      <c r="C197" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>402</v>
+      </c>
+      <c r="B198" t="s">
+        <v>849</v>
+      </c>
+      <c r="C198" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>403</v>
+      </c>
+      <c r="B199" t="s">
+        <v>828</v>
+      </c>
+      <c r="C199" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>404</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C200" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>405</v>
+      </c>
+      <c r="B201" t="s">
+        <v>829</v>
+      </c>
+      <c r="C201" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>406</v>
+      </c>
+      <c r="B202" t="s">
+        <v>826</v>
+      </c>
+      <c r="C202" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>407</v>
+      </c>
+      <c r="B203" t="s">
+        <v>804</v>
+      </c>
+      <c r="C203" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>409</v>
+      </c>
+      <c r="B204" t="s">
+        <v>841</v>
+      </c>
+      <c r="C204" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>410</v>
+      </c>
+      <c r="B205" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C205" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>411</v>
+      </c>
+      <c r="B206" t="s">
+        <v>830</v>
+      </c>
+      <c r="C206" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>412</v>
+      </c>
+      <c r="B207" t="s">
+        <v>820</v>
+      </c>
+      <c r="C207" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>413</v>
+      </c>
+      <c r="B208" t="s">
+        <v>831</v>
+      </c>
+      <c r="C208" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>414</v>
+      </c>
+      <c r="B209" t="s">
+        <v>832</v>
+      </c>
+      <c r="C209" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>415</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>416</v>
+      </c>
+      <c r="B211" t="s">
+        <v>777</v>
+      </c>
+      <c r="C211" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>417</v>
+      </c>
+      <c r="B212" t="s">
+        <v>777</v>
+      </c>
+      <c r="C212" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>418</v>
+      </c>
+      <c r="B213" t="s">
+        <v>833</v>
+      </c>
+      <c r="C213" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>419</v>
+      </c>
+      <c r="B214" t="s">
+        <v>847</v>
+      </c>
+      <c r="C214" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>420</v>
+      </c>
+      <c r="B215" t="s">
+        <v>779</v>
+      </c>
+      <c r="C215" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>421</v>
+      </c>
+      <c r="B216" t="s">
+        <v>778</v>
+      </c>
+      <c r="C216" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>422</v>
+      </c>
+      <c r="B217" t="s">
+        <v>771</v>
+      </c>
+      <c r="C217" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>423</v>
+      </c>
+      <c r="B218" t="s">
+        <v>826</v>
+      </c>
+      <c r="C218" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>424</v>
+      </c>
+      <c r="B219" t="s">
+        <v>797</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>425</v>
+      </c>
+      <c r="B220" t="s">
+        <v>834</v>
+      </c>
+      <c r="C220" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>426</v>
+      </c>
+      <c r="B221" t="s">
+        <v>807</v>
+      </c>
+      <c r="C221" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>427</v>
+      </c>
+      <c r="B222" t="s">
+        <v>809</v>
+      </c>
+      <c r="C222" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>428</v>
+      </c>
+      <c r="B223" t="s">
+        <v>835</v>
+      </c>
+      <c r="C223" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>429</v>
+      </c>
+      <c r="B224" t="s">
+        <v>836</v>
+      </c>
+      <c r="C224" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>430</v>
+      </c>
+      <c r="B225" t="s">
+        <v>815</v>
+      </c>
+      <c r="C225" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>432</v>
+      </c>
+      <c r="B226" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C226" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>433</v>
+      </c>
+      <c r="B227" t="s">
+        <v>847</v>
+      </c>
+      <c r="C227" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>434</v>
+      </c>
+      <c r="B228" t="s">
+        <v>811</v>
+      </c>
+      <c r="C228" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>435</v>
+      </c>
+      <c r="B229" t="s">
+        <v>837</v>
+      </c>
+      <c r="C229" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>436</v>
+      </c>
+      <c r="B230" t="s">
+        <v>838</v>
+      </c>
+      <c r="C230" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>437</v>
+      </c>
+      <c r="B231" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C231" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>438</v>
+      </c>
+      <c r="B232" t="s">
+        <v>779</v>
+      </c>
+      <c r="C232" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>440</v>
+      </c>
+      <c r="B233" t="s">
+        <v>790</v>
+      </c>
+      <c r="C233" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>441</v>
+      </c>
+      <c r="B234" t="s">
+        <v>827</v>
+      </c>
+      <c r="C234" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>442</v>
+      </c>
+      <c r="B235" t="s">
+        <v>785</v>
+      </c>
+      <c r="C235" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>443</v>
+      </c>
+      <c r="B236" t="s">
+        <v>843</v>
+      </c>
+      <c r="C236" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>444</v>
+      </c>
+      <c r="B237" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C237" t="s">
+        <v>917</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="C1:C1000" xr:uid="{20F1F7E7-608A-4374-928A-8F3661ADB9B1}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A2716B-33D7-4AA7-B1E2-77B338B7B220}">
   <dimension ref="A1:C281"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13174,7 +15854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB86576-3B5B-4E17-97A6-78E2002A3D74}">
   <dimension ref="A1:B232"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/spreadsheet.xlsx
+++ b/spreadsheet.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loren\Desktop\MK1212-website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C22842-C87A-4F37-9C87-C514B1AA7BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74FBF958-6B03-4F8A-B721-C83384DA3E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2003C0B9-FD41-4D78-AC63-D37F7559A3C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="Foglio4" sheetId="4" r:id="rId2"/>
-    <sheet name="Foglio2" sheetId="2" r:id="rId3"/>
-    <sheet name="Foglio3" sheetId="3" r:id="rId4"/>
+    <sheet name="Foglio5" sheetId="5" r:id="rId2"/>
+    <sheet name="Foglio4" sheetId="4" r:id="rId3"/>
+    <sheet name="Foglio2" sheetId="2" r:id="rId4"/>
+    <sheet name="Foglio3" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$D$552</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Foglio4!$C$1:$C$1000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Foglio4!$C$1:$C$1000</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3519" uniqueCount="1517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4013" uniqueCount="1519">
   <si>
     <t>false</t>
   </si>
@@ -4594,6 +4595,12 @@
   </si>
   <si>
     <t>Masovia</t>
+  </si>
+  <si>
+    <t>Marinids</t>
+  </si>
+  <si>
+    <t>Denmark</t>
   </si>
 </sst>
 </file>
@@ -6519,7 +6526,7 @@
         <v>544</v>
       </c>
       <c r="E77" t="s">
-        <v>864</v>
+        <v>1517</v>
       </c>
       <c r="F77" t="s">
         <v>1349</v>
@@ -6779,7 +6786,7 @@
         <v>557</v>
       </c>
       <c r="E90" t="s">
-        <v>915</v>
+        <v>1518</v>
       </c>
       <c r="F90" t="s">
         <v>1375</v>
@@ -10132,6 +10139,2076 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C924B66-FAAE-47D9-9F08-B405A70AE5DB}">
+  <dimension ref="A1:B257"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B13" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B18" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>197</v>
+      </c>
+      <c r="B20" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B24" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>203</v>
+      </c>
+      <c r="B25" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>204</v>
+      </c>
+      <c r="B26" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>205</v>
+      </c>
+      <c r="B27" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>206</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>207</v>
+      </c>
+      <c r="B29" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>208</v>
+      </c>
+      <c r="B30" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>209</v>
+      </c>
+      <c r="B31" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>210</v>
+      </c>
+      <c r="B32" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>211</v>
+      </c>
+      <c r="B33" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>214</v>
+      </c>
+      <c r="B35" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>215</v>
+      </c>
+      <c r="B36" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>216</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>218</v>
+      </c>
+      <c r="B38" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>219</v>
+      </c>
+      <c r="B39" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>220</v>
+      </c>
+      <c r="B40" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>221</v>
+      </c>
+      <c r="B41" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>222</v>
+      </c>
+      <c r="B42" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>223</v>
+      </c>
+      <c r="B43" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>224</v>
+      </c>
+      <c r="B44" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>225</v>
+      </c>
+      <c r="B45" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>226</v>
+      </c>
+      <c r="B46" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>228</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>229</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>230</v>
+      </c>
+      <c r="B50" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>231</v>
+      </c>
+      <c r="B51" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>232</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>233</v>
+      </c>
+      <c r="B53" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>234</v>
+      </c>
+      <c r="B54" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>235</v>
+      </c>
+      <c r="B55" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>236</v>
+      </c>
+      <c r="B56" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>237</v>
+      </c>
+      <c r="B57" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>238</v>
+      </c>
+      <c r="B58" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>239</v>
+      </c>
+      <c r="B59" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>240</v>
+      </c>
+      <c r="B60" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>241</v>
+      </c>
+      <c r="B61" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>242</v>
+      </c>
+      <c r="B62" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>243</v>
+      </c>
+      <c r="B63" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>244</v>
+      </c>
+      <c r="B64" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>246</v>
+      </c>
+      <c r="B65" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>247</v>
+      </c>
+      <c r="B66" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>248</v>
+      </c>
+      <c r="B67" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>249</v>
+      </c>
+      <c r="B68" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>250</v>
+      </c>
+      <c r="B69" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>251</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>252</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>253</v>
+      </c>
+      <c r="B72" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>255</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>256</v>
+      </c>
+      <c r="B74" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>257</v>
+      </c>
+      <c r="B75" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>258</v>
+      </c>
+      <c r="B76" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>259</v>
+      </c>
+      <c r="B77" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>260</v>
+      </c>
+      <c r="B78" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>261</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>262</v>
+      </c>
+      <c r="B80" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>263</v>
+      </c>
+      <c r="B81" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>264</v>
+      </c>
+      <c r="B82" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>265</v>
+      </c>
+      <c r="B83" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>266</v>
+      </c>
+      <c r="B84" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>268</v>
+      </c>
+      <c r="B85" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>269</v>
+      </c>
+      <c r="B86" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>270</v>
+      </c>
+      <c r="B87" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>271</v>
+      </c>
+      <c r="B88" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>272</v>
+      </c>
+      <c r="B89" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>273</v>
+      </c>
+      <c r="B90" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>274</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>275</v>
+      </c>
+      <c r="B92" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>276</v>
+      </c>
+      <c r="B93" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>278</v>
+      </c>
+      <c r="B94" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>279</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>280</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>281</v>
+      </c>
+      <c r="B97" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>283</v>
+      </c>
+      <c r="B98" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>284</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>285</v>
+      </c>
+      <c r="B100" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>287</v>
+      </c>
+      <c r="B101" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>289</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>290</v>
+      </c>
+      <c r="B103" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>291</v>
+      </c>
+      <c r="B104" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>292</v>
+      </c>
+      <c r="B105" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>293</v>
+      </c>
+      <c r="B106" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>294</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>295</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>297</v>
+      </c>
+      <c r="B109" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>298</v>
+      </c>
+      <c r="B110" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>299</v>
+      </c>
+      <c r="B111" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>300</v>
+      </c>
+      <c r="B112" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>301</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>302</v>
+      </c>
+      <c r="B114" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>303</v>
+      </c>
+      <c r="B115" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>304</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>306</v>
+      </c>
+      <c r="B117" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>307</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>309</v>
+      </c>
+      <c r="B119" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>310</v>
+      </c>
+      <c r="B120" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>311</v>
+      </c>
+      <c r="B121" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>312</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>313</v>
+      </c>
+      <c r="B123" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>314</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>315</v>
+      </c>
+      <c r="B125" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>316</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>317</v>
+      </c>
+      <c r="B127" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>318</v>
+      </c>
+      <c r="B128" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>319</v>
+      </c>
+      <c r="B129" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>320</v>
+      </c>
+      <c r="B130" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>322</v>
+      </c>
+      <c r="B131" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>323</v>
+      </c>
+      <c r="B132" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>324</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>325</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>326</v>
+      </c>
+      <c r="B135" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>327</v>
+      </c>
+      <c r="B136" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>328</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>330</v>
+      </c>
+      <c r="B138" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>331</v>
+      </c>
+      <c r="B139" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>332</v>
+      </c>
+      <c r="B140" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>334</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>335</v>
+      </c>
+      <c r="B142" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>336</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>337</v>
+      </c>
+      <c r="B144" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>338</v>
+      </c>
+      <c r="B145" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>339</v>
+      </c>
+      <c r="B146" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>341</v>
+      </c>
+      <c r="B147" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>343</v>
+      </c>
+      <c r="B148" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>344</v>
+      </c>
+      <c r="B149" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>345</v>
+      </c>
+      <c r="B150" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>347</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>348</v>
+      </c>
+      <c r="B152" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>349</v>
+      </c>
+      <c r="B153" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>350</v>
+      </c>
+      <c r="B154" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>351</v>
+      </c>
+      <c r="B155" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>352</v>
+      </c>
+      <c r="B156" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>354</v>
+      </c>
+      <c r="B157" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>355</v>
+      </c>
+      <c r="B158" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>356</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>358</v>
+      </c>
+      <c r="B160" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>359</v>
+      </c>
+      <c r="B161" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>361</v>
+      </c>
+      <c r="B162" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>362</v>
+      </c>
+      <c r="B163" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>363</v>
+      </c>
+      <c r="B164" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>364</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>365</v>
+      </c>
+      <c r="B166" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>366</v>
+      </c>
+      <c r="B167" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>367</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>368</v>
+      </c>
+      <c r="B169" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>369</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>370</v>
+      </c>
+      <c r="B171" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>371</v>
+      </c>
+      <c r="B172" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>372</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>373</v>
+      </c>
+      <c r="B174" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>374</v>
+      </c>
+      <c r="B175" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>376</v>
+      </c>
+      <c r="B176" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>377</v>
+      </c>
+      <c r="B177" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>378</v>
+      </c>
+      <c r="B178" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>379</v>
+      </c>
+      <c r="B179" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>381</v>
+      </c>
+      <c r="B180" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>382</v>
+      </c>
+      <c r="B181" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>384</v>
+      </c>
+      <c r="B182" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>385</v>
+      </c>
+      <c r="B183" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>386</v>
+      </c>
+      <c r="B184" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>387</v>
+      </c>
+      <c r="B185" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>388</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>389</v>
+      </c>
+      <c r="B187" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>390</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>391</v>
+      </c>
+      <c r="B189" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>392</v>
+      </c>
+      <c r="B190" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>393</v>
+      </c>
+      <c r="B191" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>394</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>396</v>
+      </c>
+      <c r="B193" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>397</v>
+      </c>
+      <c r="B194" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>398</v>
+      </c>
+      <c r="B195" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>400</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>401</v>
+      </c>
+      <c r="B197" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>402</v>
+      </c>
+      <c r="B198" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>403</v>
+      </c>
+      <c r="B199" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>404</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>405</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>406</v>
+      </c>
+      <c r="B202" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>407</v>
+      </c>
+      <c r="B203" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>408</v>
+      </c>
+      <c r="B204" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>409</v>
+      </c>
+      <c r="B205" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>410</v>
+      </c>
+      <c r="B206" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>411</v>
+      </c>
+      <c r="B207" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>412</v>
+      </c>
+      <c r="B208" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>413</v>
+      </c>
+      <c r="B209" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>414</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>415</v>
+      </c>
+      <c r="B211" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>416</v>
+      </c>
+      <c r="B212" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>417</v>
+      </c>
+      <c r="B213" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>418</v>
+      </c>
+      <c r="B214" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>419</v>
+      </c>
+      <c r="B215" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>420</v>
+      </c>
+      <c r="B216" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>421</v>
+      </c>
+      <c r="B217" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>422</v>
+      </c>
+      <c r="B218" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>423</v>
+      </c>
+      <c r="B219" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>424</v>
+      </c>
+      <c r="B220" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>425</v>
+      </c>
+      <c r="B221" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>426</v>
+      </c>
+      <c r="B222" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>427</v>
+      </c>
+      <c r="B223" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>428</v>
+      </c>
+      <c r="B224" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>429</v>
+      </c>
+      <c r="B225" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>430</v>
+      </c>
+      <c r="B226" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>432</v>
+      </c>
+      <c r="B227" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>433</v>
+      </c>
+      <c r="B228" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>434</v>
+      </c>
+      <c r="B229" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>435</v>
+      </c>
+      <c r="B230" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>436</v>
+      </c>
+      <c r="B231" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>437</v>
+      </c>
+      <c r="B232" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>438</v>
+      </c>
+      <c r="B233" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>440</v>
+      </c>
+      <c r="B234" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>441</v>
+      </c>
+      <c r="B235" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>442</v>
+      </c>
+      <c r="B236" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>443</v>
+      </c>
+      <c r="B237" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>444</v>
+      </c>
+      <c r="B238" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>445</v>
+      </c>
+      <c r="B239" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>446</v>
+      </c>
+      <c r="B240" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>447</v>
+      </c>
+      <c r="B241" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>448</v>
+      </c>
+      <c r="B242" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>449</v>
+      </c>
+      <c r="B243" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>450</v>
+      </c>
+      <c r="B244" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>451</v>
+      </c>
+      <c r="B245" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>452</v>
+      </c>
+      <c r="B246" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>453</v>
+      </c>
+      <c r="B247" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>454</v>
+      </c>
+      <c r="B248" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>455</v>
+      </c>
+      <c r="B249" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>456</v>
+      </c>
+      <c r="B250" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>457</v>
+      </c>
+      <c r="B251" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>458</v>
+      </c>
+      <c r="B252" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>459</v>
+      </c>
+      <c r="B253" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>461</v>
+      </c>
+      <c r="B254" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>462</v>
+      </c>
+      <c r="B255" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>463</v>
+      </c>
+      <c r="B256" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>465</v>
+      </c>
+      <c r="B257" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20F1F7E7-608A-4374-928A-8F3661ADB9B1}">
   <dimension ref="A1:C237"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12750,7 +14827,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A2716B-33D7-4AA7-B1E2-77B338B7B220}">
   <dimension ref="A1:C281"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15854,7 +17931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB86576-3B5B-4E17-97A6-78E2002A3D74}">
   <dimension ref="A1:B232"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/spreadsheet.xlsx
+++ b/spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loren\Desktop\MK1212-website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74FBF958-6B03-4F8A-B721-C83384DA3E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199B9859-2139-43EC-9AE1-FE7E9E5A69EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2003C0B9-FD41-4D78-AC63-D37F7559A3C6}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4013" uniqueCount="1519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4013" uniqueCount="1520">
   <si>
     <t>false</t>
   </si>
@@ -4601,6 +4601,9 @@
   </si>
   <si>
     <t>Denmark</t>
+  </si>
+  <si>
+    <t>Zaydi</t>
   </si>
 </sst>
 </file>
@@ -6986,7 +6989,7 @@
         <v>567</v>
       </c>
       <c r="E100" t="s">
-        <v>926</v>
+        <v>904</v>
       </c>
       <c r="F100" t="s">
         <v>1391</v>
@@ -7466,7 +7469,7 @@
         <v>591</v>
       </c>
       <c r="E124" t="s">
-        <v>1509</v>
+        <v>1519</v>
       </c>
       <c r="F124" t="s">
         <v>1349</v>
@@ -10135,6 +10138,7 @@
   </sheetData>
   <autoFilter ref="A1:D552" xr:uid="{EB689665-45D9-42F4-AA4C-1FD1A1AE5053}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
